--- a/output/final/geo/geo distributors (status checked)/geo_powerline_utility_drone_verified_distributors.xlsx
+++ b/output/final/geo/geo distributors (status checked)/geo_powerline_utility_drone_verified_distributors.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Companies" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Companies'!$A$5:$U$206</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Companies'!$A$5:$U$205</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Companies'!$5:$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -597,7 +597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:U206"/>
+  <dimension ref="A1:U205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -647,7 +647,7 @@
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>Distributors listed: 201     |     Headquarter countries: 1     |     Acquired by another group (named in the company name): 4</t>
+          <t>Distributors listed: 200     |     Headquarter countries: 1     |     Acquired by another group (named in the company name): 4</t>
         </is>
       </c>
     </row>
@@ -11868,20 +11868,20 @@
       </c>
       <c r="B138" s="12" t="inlineStr">
         <is>
-          <t>Magic Myna Private Limited</t>
+          <t>Green World Soft Tech</t>
         </is>
       </c>
       <c r="C138" s="13" t="inlineStr">
         <is>
-          <t>https://magicmyna.com</t>
+          <t>http://www.gworld.tech</t>
         </is>
       </c>
       <c r="D138" s="11" t="n">
-        <v>2020</v>
+        <v>2024</v>
       </c>
       <c r="E138" s="14" t="inlineStr">
         <is>
-          <t>Coimbatore, India</t>
+          <t>Chennai, India</t>
         </is>
       </c>
       <c r="F138" s="14" t="inlineStr">
@@ -11901,27 +11901,27 @@
       </c>
       <c r="I138" s="11" t="inlineStr">
         <is>
-          <t>10-50</t>
+          <t>1-20</t>
         </is>
       </c>
       <c r="J138" s="14" t="inlineStr">
         <is>
-          <t>Aerial utility inspection; drone survey operations</t>
+          <t>Field data collection apps; GIS network mapping services</t>
         </is>
       </c>
       <c r="K138" s="14" t="inlineStr">
         <is>
-          <t>Third-party aerial surveillance and transmission corridor survey services across industrial utility assets</t>
+          <t>Providing digital mapping workflows and field asset logging platforms for electrical distribution systems</t>
         </is>
       </c>
       <c r="L138" s="14" t="inlineStr">
         <is>
-          <t>Drone power line thermal mapping payloads</t>
+          <t>Offline GIS mapping integration and drone data pipeline analytics tools</t>
         </is>
       </c>
       <c r="M138" s="11" t="inlineStr">
         <is>
-          <t>Offline</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="N138" s="14" t="inlineStr"/>
@@ -11931,7 +11931,7 @@
       <c r="R138" s="14" t="inlineStr"/>
       <c r="S138" s="13" t="inlineStr">
         <is>
-          <t>https://magicmyna.com</t>
+          <t>http://www.gworld.tech</t>
         </is>
       </c>
       <c r="T138" s="14" t="inlineStr"/>
@@ -11941,22 +11941,22 @@
         </is>
       </c>
     </row>
-    <row r="139" ht="46.5" customHeight="1">
+    <row r="139" ht="33" customHeight="1">
       <c r="A139" s="15" t="n">
         <v>134</v>
       </c>
       <c r="B139" s="16" t="inlineStr">
         <is>
-          <t>Green World Soft Tech</t>
+          <t>Velciti Consulting Engineers Private Limited</t>
         </is>
       </c>
       <c r="C139" s="17" t="inlineStr">
         <is>
-          <t>http://www.gworld.tech</t>
+          <t>velciti.com</t>
         </is>
       </c>
       <c r="D139" s="15" t="n">
-        <v>2024</v>
+        <v>2017</v>
       </c>
       <c r="E139" s="18" t="inlineStr">
         <is>
@@ -11980,22 +11980,22 @@
       </c>
       <c r="I139" s="15" t="inlineStr">
         <is>
-          <t>1-20</t>
+          <t>11-50</t>
         </is>
       </c>
       <c r="J139" s="18" t="inlineStr">
         <is>
-          <t>Field data collection apps; GIS network mapping services</t>
+          <t>Infrastructure consultancy programs; drone topographic mapping</t>
         </is>
       </c>
       <c r="K139" s="18" t="inlineStr">
         <is>
-          <t>Providing digital mapping workflows and field asset logging platforms for electrical distribution systems</t>
+          <t>Utility network routing alignment and digital corridor asset tracing</t>
         </is>
       </c>
       <c r="L139" s="18" t="inlineStr">
         <is>
-          <t>Offline GIS mapping integration and drone data pipeline analytics tools</t>
+          <t>Photogrammetry software trackers; DGPS layout systems; digital elevation profiling</t>
         </is>
       </c>
       <c r="M139" s="15" t="inlineStr">
@@ -12010,7 +12010,7 @@
       <c r="R139" s="18" t="inlineStr"/>
       <c r="S139" s="17" t="inlineStr">
         <is>
-          <t>http://www.gworld.tech</t>
+          <t>velciti.com</t>
         </is>
       </c>
       <c r="T139" s="18" t="inlineStr"/>
@@ -12026,16 +12026,16 @@
       </c>
       <c r="B140" s="12" t="inlineStr">
         <is>
-          <t>Velciti Consulting Engineers Private Limited</t>
+          <t>Hawking UAV</t>
         </is>
       </c>
       <c r="C140" s="13" t="inlineStr">
         <is>
-          <t>velciti.com</t>
+          <t>hawking.in</t>
         </is>
       </c>
       <c r="D140" s="11" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="E140" s="14" t="inlineStr">
         <is>
@@ -12064,17 +12064,17 @@
       </c>
       <c r="J140" s="14" t="inlineStr">
         <is>
-          <t>Infrastructure consultancy programs; drone topographic mapping</t>
+          <t>Unmanned aerial systems; Industrial asset inspection</t>
         </is>
       </c>
       <c r="K140" s="14" t="inlineStr">
         <is>
-          <t>Utility network routing alignment and digital corridor asset tracing</t>
+          <t>Utility asset mapping and thermal geospatial data processing</t>
         </is>
       </c>
       <c r="L140" s="14" t="inlineStr">
         <is>
-          <t>Photogrammetry software trackers; DGPS layout systems; digital elevation profiling</t>
+          <t>Aerial transmission line inspection, thermal analytics, and LiDAR data processing</t>
         </is>
       </c>
       <c r="M140" s="11" t="inlineStr">
@@ -12082,14 +12082,22 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="N140" s="14" t="inlineStr"/>
-      <c r="O140" s="14" t="inlineStr"/>
+      <c r="N140" s="14" t="inlineStr">
+        <is>
+          <t>Dhinesh Thangavelu</t>
+        </is>
+      </c>
+      <c r="O140" s="14" t="inlineStr">
+        <is>
+          <t>Founder &amp; CEO</t>
+        </is>
+      </c>
       <c r="P140" s="14" t="inlineStr"/>
       <c r="Q140" s="14" t="inlineStr"/>
       <c r="R140" s="14" t="inlineStr"/>
       <c r="S140" s="13" t="inlineStr">
         <is>
-          <t>velciti.com</t>
+          <t>hawking.in</t>
         </is>
       </c>
       <c r="T140" s="14" t="inlineStr"/>
@@ -12105,16 +12113,16 @@
       </c>
       <c r="B141" s="16" t="inlineStr">
         <is>
-          <t>Hawking UAV</t>
+          <t>Bennysurya Venture Private Limited</t>
         </is>
       </c>
       <c r="C141" s="17" t="inlineStr">
         <is>
-          <t>hawking.in</t>
+          <t>accuratetopomappers.com</t>
         </is>
       </c>
       <c r="D141" s="15" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="E141" s="18" t="inlineStr">
         <is>
@@ -12143,17 +12151,17 @@
       </c>
       <c r="J141" s="18" t="inlineStr">
         <is>
-          <t>Unmanned aerial systems; Industrial asset inspection</t>
+          <t>Industrial drone inspections; Thermal imaging; Volumetric surveys</t>
         </is>
       </c>
       <c r="K141" s="18" t="inlineStr">
         <is>
-          <t>Utility asset mapping and thermal geospatial data processing</t>
+          <t>Thermal fault detection and overhead corridor inspection</t>
         </is>
       </c>
       <c r="L141" s="18" t="inlineStr">
         <is>
-          <t>Aerial transmission line inspection, thermal analytics, and LiDAR data processing</t>
+          <t>Drone thermography for power lines and LiDAR asset modeling</t>
         </is>
       </c>
       <c r="M141" s="15" t="inlineStr">
@@ -12161,22 +12169,14 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="N141" s="18" t="inlineStr">
-        <is>
-          <t>Dhinesh Thangavelu</t>
-        </is>
-      </c>
-      <c r="O141" s="18" t="inlineStr">
-        <is>
-          <t>Founder &amp; CEO</t>
-        </is>
-      </c>
+      <c r="N141" s="18" t="inlineStr"/>
+      <c r="O141" s="18" t="inlineStr"/>
       <c r="P141" s="18" t="inlineStr"/>
       <c r="Q141" s="18" t="inlineStr"/>
       <c r="R141" s="18" t="inlineStr"/>
       <c r="S141" s="17" t="inlineStr">
         <is>
-          <t>hawking.in</t>
+          <t>accuratetopomappers.com</t>
         </is>
       </c>
       <c r="T141" s="18" t="inlineStr"/>
@@ -12192,16 +12192,16 @@
       </c>
       <c r="B142" s="12" t="inlineStr">
         <is>
-          <t>Bennysurya Venture Private Limited</t>
+          <t>Mars Synergy Geo Tech Private Limited</t>
         </is>
       </c>
       <c r="C142" s="13" t="inlineStr">
         <is>
-          <t>accuratetopomappers.com</t>
+          <t>marssynergygeotech.com</t>
         </is>
       </c>
       <c r="D142" s="11" t="n">
-        <v>2019</v>
+        <v>2009</v>
       </c>
       <c r="E142" s="14" t="inlineStr">
         <is>
@@ -12225,22 +12225,22 @@
       </c>
       <c r="I142" s="11" t="inlineStr">
         <is>
-          <t>11-50</t>
+          <t>25-50</t>
         </is>
       </c>
       <c r="J142" s="14" t="inlineStr">
         <is>
-          <t>Industrial drone inspections; Thermal imaging; Volumetric surveys</t>
+          <t>Geotechnical investigation; Drone mapping; Topographic surveys</t>
         </is>
       </c>
       <c r="K142" s="14" t="inlineStr">
         <is>
-          <t>Thermal fault detection and overhead corridor inspection</t>
+          <t>Overhead infrastructure tracking and aerial geospatial profiling</t>
         </is>
       </c>
       <c r="L142" s="14" t="inlineStr">
         <is>
-          <t>Drone thermography for power lines and LiDAR asset modeling</t>
+          <t>UAV corridor mapping and digital elevation modeling for utilities</t>
         </is>
       </c>
       <c r="M142" s="11" t="inlineStr">
@@ -12248,17 +12248,37 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="N142" s="14" t="inlineStr"/>
-      <c r="O142" s="14" t="inlineStr"/>
-      <c r="P142" s="14" t="inlineStr"/>
+      <c r="N142" s="14" t="inlineStr">
+        <is>
+          <t>Baskar</t>
+        </is>
+      </c>
+      <c r="O142" s="14" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="P142" s="13" t="inlineStr">
+        <is>
+          <t>finance@msgeotech.com</t>
+        </is>
+      </c>
       <c r="Q142" s="14" t="inlineStr"/>
-      <c r="R142" s="14" t="inlineStr"/>
+      <c r="R142" s="14" t="inlineStr">
+        <is>
+          <t>+917942557489</t>
+        </is>
+      </c>
       <c r="S142" s="13" t="inlineStr">
         <is>
-          <t>accuratetopomappers.com</t>
-        </is>
-      </c>
-      <c r="T142" s="14" t="inlineStr"/>
+          <t>marssynergygeotech.com</t>
+        </is>
+      </c>
+      <c r="T142" s="13" t="inlineStr">
+        <is>
+          <t>finance@msgeotech.com</t>
+        </is>
+      </c>
       <c r="U142" s="11" t="inlineStr">
         <is>
           <t>+91 / IN</t>
@@ -12271,20 +12291,20 @@
       </c>
       <c r="B143" s="16" t="inlineStr">
         <is>
-          <t>Mars Synergy Geo Tech Private Limited</t>
+          <t>RevDrones Technologies Pvt. Ltd.</t>
         </is>
       </c>
       <c r="C143" s="17" t="inlineStr">
         <is>
-          <t>marssynergygeotech.com</t>
+          <t>revdrones.in</t>
         </is>
       </c>
       <c r="D143" s="15" t="n">
-        <v>2009</v>
+        <v>2023</v>
       </c>
       <c r="E143" s="18" t="inlineStr">
         <is>
-          <t>Chennai, India</t>
+          <t>Vadodara, India</t>
         </is>
       </c>
       <c r="F143" s="18" t="inlineStr">
@@ -12304,22 +12324,22 @@
       </c>
       <c r="I143" s="15" t="inlineStr">
         <is>
-          <t>25-50</t>
+          <t>2-10</t>
         </is>
       </c>
       <c r="J143" s="18" t="inlineStr">
         <is>
-          <t>Geotechnical investigation; Drone mapping; Topographic surveys</t>
+          <t>Industrial drone surveys; Computer vision intelligence</t>
         </is>
       </c>
       <c r="K143" s="18" t="inlineStr">
         <is>
-          <t>Overhead infrastructure tracking and aerial geospatial profiling</t>
+          <t>Automated computer vision defect reporting for utility assets</t>
         </is>
       </c>
       <c r="L143" s="18" t="inlineStr">
         <is>
-          <t>UAV corridor mapping and digital elevation modeling for utilities</t>
+          <t>AI automated defect reporting, aerial LiDAR diagnostics</t>
         </is>
       </c>
       <c r="M143" s="15" t="inlineStr">
@@ -12327,37 +12347,17 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="N143" s="18" t="inlineStr">
-        <is>
-          <t>Baskar</t>
-        </is>
-      </c>
-      <c r="O143" s="18" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="P143" s="17" t="inlineStr">
-        <is>
-          <t>finance@msgeotech.com</t>
-        </is>
-      </c>
+      <c r="N143" s="18" t="inlineStr"/>
+      <c r="O143" s="18" t="inlineStr"/>
+      <c r="P143" s="18" t="inlineStr"/>
       <c r="Q143" s="18" t="inlineStr"/>
-      <c r="R143" s="18" t="inlineStr">
-        <is>
-          <t>+917942557489</t>
-        </is>
-      </c>
+      <c r="R143" s="18" t="inlineStr"/>
       <c r="S143" s="17" t="inlineStr">
         <is>
-          <t>marssynergygeotech.com</t>
-        </is>
-      </c>
-      <c r="T143" s="17" t="inlineStr">
-        <is>
-          <t>finance@msgeotech.com</t>
-        </is>
-      </c>
+          <t>revdrones.in</t>
+        </is>
+      </c>
+      <c r="T143" s="18" t="inlineStr"/>
       <c r="U143" s="15" t="inlineStr">
         <is>
           <t>+91 / IN</t>
@@ -12370,16 +12370,16 @@
       </c>
       <c r="B144" s="12" t="inlineStr">
         <is>
-          <t>RevDrones Technologies Pvt. Ltd.</t>
+          <t>Sky2Earth Technology</t>
         </is>
       </c>
       <c r="C144" s="13" t="inlineStr">
         <is>
-          <t>revdrones.in</t>
+          <t>sky2earth.in</t>
         </is>
       </c>
       <c r="D144" s="11" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="E144" s="14" t="inlineStr">
         <is>
@@ -12403,37 +12403,45 @@
       </c>
       <c r="I144" s="11" t="inlineStr">
         <is>
-          <t>2-10</t>
+          <t>11-50</t>
         </is>
       </c>
       <c r="J144" s="14" t="inlineStr">
         <is>
-          <t>Industrial drone surveys; Computer vision intelligence</t>
+          <t>Drone data mapping; Geographic Information Systems (GIS)</t>
         </is>
       </c>
       <c r="K144" s="14" t="inlineStr">
         <is>
-          <t>Automated computer vision defect reporting for utility assets</t>
+          <t>High-precision topographic mapping and thermal inspection for utility sectors</t>
         </is>
       </c>
       <c r="L144" s="14" t="inlineStr">
         <is>
-          <t>AI automated defect reporting, aerial LiDAR diagnostics</t>
+          <t>Aerial thermography sensors, cm-level accuracy photogrammetry</t>
         </is>
       </c>
       <c r="M144" s="11" t="inlineStr">
         <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="N144" s="14" t="inlineStr"/>
-      <c r="O144" s="14" t="inlineStr"/>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="N144" s="14" t="inlineStr">
+        <is>
+          <t>Vinod Kewat</t>
+        </is>
+      </c>
+      <c r="O144" s="14" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
       <c r="P144" s="14" t="inlineStr"/>
       <c r="Q144" s="14" t="inlineStr"/>
       <c r="R144" s="14" t="inlineStr"/>
       <c r="S144" s="13" t="inlineStr">
         <is>
-          <t>revdrones.in</t>
+          <t>sky2earth.in</t>
         </is>
       </c>
       <c r="T144" s="14" t="inlineStr"/>
@@ -12449,16 +12457,16 @@
       </c>
       <c r="B145" s="16" t="inlineStr">
         <is>
-          <t>Sky2Earth Technology</t>
+          <t>Naksha Innovative Solutions</t>
         </is>
       </c>
       <c r="C145" s="17" t="inlineStr">
         <is>
-          <t>sky2earth.in</t>
+          <t>https://www.nakshageotech.com</t>
         </is>
       </c>
       <c r="D145" s="15" t="n">
-        <v>2022</v>
+        <v>2010</v>
       </c>
       <c r="E145" s="18" t="inlineStr">
         <is>
@@ -12482,22 +12490,22 @@
       </c>
       <c r="I145" s="15" t="inlineStr">
         <is>
-          <t>11-50</t>
+          <t>2-10</t>
         </is>
       </c>
       <c r="J145" s="18" t="inlineStr">
         <is>
-          <t>Drone data mapping; Geographic Information Systems (GIS)</t>
+          <t>Topographic land mapping; 3D asset inspection</t>
         </is>
       </c>
       <c r="K145" s="18" t="inlineStr">
         <is>
-          <t>High-precision topographic mapping and thermal inspection for utility sectors</t>
+          <t>LiDAR and photogrammetry workflows for distribution line mapping</t>
         </is>
       </c>
       <c r="L145" s="18" t="inlineStr">
         <is>
-          <t>Aerial thermography sensors, cm-level accuracy photogrammetry</t>
+          <t>3D point cloud generation, drone photogrammetry suites</t>
         </is>
       </c>
       <c r="M145" s="15" t="inlineStr">
@@ -12507,12 +12515,12 @@
       </c>
       <c r="N145" s="18" t="inlineStr">
         <is>
-          <t>Vinod Kewat</t>
+          <t>Jay Gohil</t>
         </is>
       </c>
       <c r="O145" s="18" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Proprietor</t>
         </is>
       </c>
       <c r="P145" s="18" t="inlineStr"/>
@@ -12520,7 +12528,7 @@
       <c r="R145" s="18" t="inlineStr"/>
       <c r="S145" s="17" t="inlineStr">
         <is>
-          <t>sky2earth.in</t>
+          <t>https://www.nakshageotech.com</t>
         </is>
       </c>
       <c r="T145" s="18" t="inlineStr"/>
@@ -12536,16 +12544,16 @@
       </c>
       <c r="B146" s="12" t="inlineStr">
         <is>
-          <t>Naksha Innovative Solutions</t>
+          <t>KVGGN Synergy</t>
         </is>
       </c>
       <c r="C146" s="13" t="inlineStr">
         <is>
-          <t>https://www.nakshageotech.com</t>
+          <t>https://kvggn.in</t>
         </is>
       </c>
       <c r="D146" s="11" t="n">
-        <v>2010</v>
+        <v>2020</v>
       </c>
       <c r="E146" s="14" t="inlineStr">
         <is>
@@ -12569,22 +12577,22 @@
       </c>
       <c r="I146" s="11" t="inlineStr">
         <is>
-          <t>2-10</t>
+          <t>11-50</t>
         </is>
       </c>
       <c r="J146" s="14" t="inlineStr">
         <is>
-          <t>Topographic land mapping; 3D asset inspection</t>
+          <t>Substation maintenance services; Power evacuation inspections</t>
         </is>
       </c>
       <c r="K146" s="14" t="inlineStr">
         <is>
-          <t>LiDAR and photogrammetry workflows for distribution line mapping</t>
+          <t>Grid operations support incorporating aerial drone diagnostics</t>
         </is>
       </c>
       <c r="L146" s="14" t="inlineStr">
         <is>
-          <t>3D point cloud generation, drone photogrammetry suites</t>
+          <t>Drone line stringing support systems, visual and aerial thermal sensors</t>
         </is>
       </c>
       <c r="M146" s="11" t="inlineStr">
@@ -12592,22 +12600,14 @@
           <t>Offline</t>
         </is>
       </c>
-      <c r="N146" s="14" t="inlineStr">
-        <is>
-          <t>Jay Gohil</t>
-        </is>
-      </c>
-      <c r="O146" s="14" t="inlineStr">
-        <is>
-          <t>Proprietor</t>
-        </is>
-      </c>
+      <c r="N146" s="14" t="inlineStr"/>
+      <c r="O146" s="14" t="inlineStr"/>
       <c r="P146" s="14" t="inlineStr"/>
       <c r="Q146" s="14" t="inlineStr"/>
       <c r="R146" s="14" t="inlineStr"/>
       <c r="S146" s="13" t="inlineStr">
         <is>
-          <t>https://www.nakshageotech.com</t>
+          <t>https://kvggn.in</t>
         </is>
       </c>
       <c r="T146" s="14" t="inlineStr"/>
@@ -12623,20 +12623,20 @@
       </c>
       <c r="B147" s="16" t="inlineStr">
         <is>
-          <t>KVGGN Synergy</t>
+          <t>Enercomp Solutions Private Limited</t>
         </is>
       </c>
       <c r="C147" s="17" t="inlineStr">
         <is>
-          <t>https://kvggn.in</t>
+          <t>https://enercomp.in</t>
         </is>
       </c>
       <c r="D147" s="15" t="n">
-        <v>2020</v>
+        <v>2013</v>
       </c>
       <c r="E147" s="18" t="inlineStr">
         <is>
-          <t>Vadodara, India</t>
+          <t>Ahmedabad, India</t>
         </is>
       </c>
       <c r="F147" s="18" t="inlineStr">
@@ -12661,22 +12661,22 @@
       </c>
       <c r="J147" s="18" t="inlineStr">
         <is>
-          <t>Substation maintenance services; Power evacuation inspections</t>
+          <t>UAV inspection services; Industrial aerial solutions</t>
         </is>
       </c>
       <c r="K147" s="18" t="inlineStr">
         <is>
-          <t>Grid operations support incorporating aerial drone diagnostics</t>
+          <t>Power transmission infrastructure condition monitoring and GIS integration</t>
         </is>
       </c>
       <c r="L147" s="18" t="inlineStr">
         <is>
-          <t>Drone line stringing support systems, visual and aerial thermal sensors</t>
+          <t>Thermal IR cameras and multirotor flight payloads</t>
         </is>
       </c>
       <c r="M147" s="15" t="inlineStr">
         <is>
-          <t>Offline</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="N147" s="18" t="inlineStr"/>
@@ -12686,7 +12686,7 @@
       <c r="R147" s="18" t="inlineStr"/>
       <c r="S147" s="17" t="inlineStr">
         <is>
-          <t>https://kvggn.in</t>
+          <t>https://enercomp.in</t>
         </is>
       </c>
       <c r="T147" s="18" t="inlineStr"/>
@@ -12702,12 +12702,12 @@
       </c>
       <c r="B148" s="12" t="inlineStr">
         <is>
-          <t>Enercomp Solutions Private Limited</t>
+          <t>Trishunya Survey Solution</t>
         </is>
       </c>
       <c r="C148" s="13" t="inlineStr">
         <is>
-          <t>https://enercomp.in</t>
+          <t>https://trishunya.com</t>
         </is>
       </c>
       <c r="D148" s="11" t="n">
@@ -12740,17 +12740,17 @@
       </c>
       <c r="J148" s="14" t="inlineStr">
         <is>
-          <t>UAV inspection services; Industrial aerial solutions</t>
+          <t>Transmission line route surveys; Drone photogrammetry</t>
         </is>
       </c>
       <c r="K148" s="14" t="inlineStr">
         <is>
-          <t>Power transmission infrastructure condition monitoring and GIS integration</t>
+          <t>Power infrastructure linear monitoring and corridor clearing analytics</t>
         </is>
       </c>
       <c r="L148" s="14" t="inlineStr">
         <is>
-          <t>Thermal IR cameras and multirotor flight payloads</t>
+          <t>UAV LiDAR and DGPS tracking units</t>
         </is>
       </c>
       <c r="M148" s="11" t="inlineStr">
@@ -12760,15 +12760,27 @@
       </c>
       <c r="N148" s="14" t="inlineStr"/>
       <c r="O148" s="14" t="inlineStr"/>
-      <c r="P148" s="14" t="inlineStr"/>
+      <c r="P148" s="13" t="inlineStr">
+        <is>
+          <t>info@trishunya.com</t>
+        </is>
+      </c>
       <c r="Q148" s="14" t="inlineStr"/>
-      <c r="R148" s="14" t="inlineStr"/>
+      <c r="R148" s="14" t="inlineStr">
+        <is>
+          <t>+91 95107 85007</t>
+        </is>
+      </c>
       <c r="S148" s="13" t="inlineStr">
         <is>
-          <t>https://enercomp.in</t>
-        </is>
-      </c>
-      <c r="T148" s="14" t="inlineStr"/>
+          <t>https://trishunya.com</t>
+        </is>
+      </c>
+      <c r="T148" s="13" t="inlineStr">
+        <is>
+          <t>info@trishunya.com</t>
+        </is>
+      </c>
       <c r="U148" s="11" t="inlineStr">
         <is>
           <t>+91 / IN</t>
@@ -12781,20 +12793,20 @@
       </c>
       <c r="B149" s="16" t="inlineStr">
         <is>
-          <t>Trishunya Survey Solution</t>
+          <t>Prime UAV</t>
         </is>
       </c>
       <c r="C149" s="17" t="inlineStr">
         <is>
-          <t>https://trishunya.com</t>
+          <t>https://primeuav.com</t>
         </is>
       </c>
       <c r="D149" s="15" t="n">
-        <v>2013</v>
+        <v>2020</v>
       </c>
       <c r="E149" s="18" t="inlineStr">
         <is>
-          <t>Ahmedabad, India</t>
+          <t>Surat, India</t>
         </is>
       </c>
       <c r="F149" s="18" t="inlineStr">
@@ -12819,17 +12831,17 @@
       </c>
       <c r="J149" s="18" t="inlineStr">
         <is>
-          <t>Transmission line route surveys; Drone photogrammetry</t>
+          <t>Industrial aerial inspection; Drone mapping</t>
         </is>
       </c>
       <c r="K149" s="18" t="inlineStr">
         <is>
-          <t>Power infrastructure linear monitoring and corridor clearing analytics</t>
+          <t>Municipal asset monitoring, infrastructure safety inspections, and thermal mapping</t>
         </is>
       </c>
       <c r="L149" s="18" t="inlineStr">
         <is>
-          <t>UAV LiDAR and DGPS tracking units</t>
+          <t>AI-enabled drone surveillance, thermal inspection payloads</t>
         </is>
       </c>
       <c r="M149" s="15" t="inlineStr">
@@ -12839,53 +12851,41 @@
       </c>
       <c r="N149" s="18" t="inlineStr"/>
       <c r="O149" s="18" t="inlineStr"/>
-      <c r="P149" s="17" t="inlineStr">
-        <is>
-          <t>info@trishunya.com</t>
-        </is>
-      </c>
+      <c r="P149" s="18" t="inlineStr"/>
       <c r="Q149" s="18" t="inlineStr"/>
-      <c r="R149" s="18" t="inlineStr">
-        <is>
-          <t>+91 95107 85007</t>
-        </is>
-      </c>
+      <c r="R149" s="18" t="inlineStr"/>
       <c r="S149" s="17" t="inlineStr">
         <is>
-          <t>https://trishunya.com</t>
-        </is>
-      </c>
-      <c r="T149" s="17" t="inlineStr">
-        <is>
-          <t>info@trishunya.com</t>
-        </is>
-      </c>
+          <t>https://primeuav.com</t>
+        </is>
+      </c>
+      <c r="T149" s="18" t="inlineStr"/>
       <c r="U149" s="15" t="inlineStr">
         <is>
           <t>+91 / IN</t>
         </is>
       </c>
     </row>
-    <row r="150" ht="33" customHeight="1">
+    <row r="150" ht="46.5" customHeight="1">
       <c r="A150" s="11" t="n">
         <v>145</v>
       </c>
       <c r="B150" s="12" t="inlineStr">
         <is>
-          <t>Prime UAV</t>
+          <t>Patel Survey Agency</t>
         </is>
       </c>
       <c r="C150" s="13" t="inlineStr">
         <is>
-          <t>https://primeuav.com</t>
+          <t>https://patelsurveyagency.com</t>
         </is>
       </c>
       <c r="D150" s="11" t="n">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="E150" s="14" t="inlineStr">
         <is>
-          <t>Surat, India</t>
+          <t>Ahmedabad, India</t>
         </is>
       </c>
       <c r="F150" s="14" t="inlineStr">
@@ -12905,40 +12905,48 @@
       </c>
       <c r="I150" s="11" t="inlineStr">
         <is>
-          <t>11-50</t>
+          <t>1-10</t>
         </is>
       </c>
       <c r="J150" s="14" t="inlineStr">
         <is>
-          <t>Industrial aerial inspection; Drone mapping</t>
+          <t>Land surveying; transmission line mapping</t>
         </is>
       </c>
       <c r="K150" s="14" t="inlineStr">
         <is>
-          <t>Municipal asset monitoring, infrastructure safety inspections, and thermal mapping</t>
+          <t>Precision aerial land scanning and geographic alignment tracking</t>
         </is>
       </c>
       <c r="L150" s="14" t="inlineStr">
         <is>
-          <t>AI-enabled drone surveillance, thermal inspection payloads</t>
+          <t>UAV photogrammetry platforms; high-resolution aerial cameras; total station tracking devices</t>
         </is>
       </c>
       <c r="M150" s="11" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Offline</t>
         </is>
       </c>
       <c r="N150" s="14" t="inlineStr"/>
       <c r="O150" s="14" t="inlineStr"/>
       <c r="P150" s="14" t="inlineStr"/>
       <c r="Q150" s="14" t="inlineStr"/>
-      <c r="R150" s="14" t="inlineStr"/>
+      <c r="R150" s="14" t="inlineStr">
+        <is>
+          <t>+91 95740 96142</t>
+        </is>
+      </c>
       <c r="S150" s="13" t="inlineStr">
         <is>
-          <t>https://primeuav.com</t>
-        </is>
-      </c>
-      <c r="T150" s="14" t="inlineStr"/>
+          <t>https://patelsurveyagency.com</t>
+        </is>
+      </c>
+      <c r="T150" s="13" t="inlineStr">
+        <is>
+          <t>info@patelsurveyors.com</t>
+        </is>
+      </c>
       <c r="U150" s="11" t="inlineStr">
         <is>
           <t>+91 / IN</t>
@@ -12951,16 +12959,16 @@
       </c>
       <c r="B151" s="16" t="inlineStr">
         <is>
-          <t>Patel Survey Agency</t>
+          <t>Tessellate Earthscan Private Limited</t>
         </is>
       </c>
       <c r="C151" s="17" t="inlineStr">
         <is>
-          <t>https://patelsurveyagency.com</t>
+          <t>https://tessellateearthscan.com</t>
         </is>
       </c>
       <c r="D151" s="15" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="E151" s="18" t="inlineStr">
         <is>
@@ -12984,27 +12992,27 @@
       </c>
       <c r="I151" s="15" t="inlineStr">
         <is>
-          <t>1-10</t>
+          <t>10-50</t>
         </is>
       </c>
       <c r="J151" s="18" t="inlineStr">
         <is>
-          <t>Land surveying; transmission line mapping</t>
+          <t>Drone surveying; infrastructure asset mapping</t>
         </is>
       </c>
       <c r="K151" s="18" t="inlineStr">
         <is>
-          <t>Precision aerial land scanning and geographic alignment tracking</t>
+          <t>Drone inspection and geospatial engineering data processing for infrastructure networks</t>
         </is>
       </c>
       <c r="L151" s="18" t="inlineStr">
         <is>
-          <t>UAV photogrammetry platforms; high-resolution aerial cameras; total station tracking devices</t>
+          <t>DGPS ground data systems; photogrammetry UAV mapping modules; digital asset rendering suites</t>
         </is>
       </c>
       <c r="M151" s="15" t="inlineStr">
         <is>
-          <t>Offline</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="N151" s="18" t="inlineStr"/>
@@ -13013,17 +13021,17 @@
       <c r="Q151" s="18" t="inlineStr"/>
       <c r="R151" s="18" t="inlineStr">
         <is>
-          <t>+91 95740 96142</t>
+          <t>+91 98258 06532</t>
         </is>
       </c>
       <c r="S151" s="17" t="inlineStr">
         <is>
-          <t>https://patelsurveyagency.com</t>
+          <t>https://tessellateearthscan.com</t>
         </is>
       </c>
       <c r="T151" s="17" t="inlineStr">
         <is>
-          <t>info@patelsurveyors.com</t>
+          <t>krishna@tessellateearthscan.com</t>
         </is>
       </c>
       <c r="U151" s="15" t="inlineStr">
@@ -13032,22 +13040,22 @@
         </is>
       </c>
     </row>
-    <row r="152" ht="46.5" customHeight="1">
+    <row r="152" ht="33" customHeight="1">
       <c r="A152" s="11" t="n">
         <v>147</v>
       </c>
       <c r="B152" s="12" t="inlineStr">
         <is>
-          <t>Tessellate Earthscan Private Limited</t>
+          <t>Akshar Consultancy</t>
         </is>
       </c>
       <c r="C152" s="13" t="inlineStr">
         <is>
-          <t>https://tessellateearthscan.com</t>
+          <t>https://aksharcon.com</t>
         </is>
       </c>
       <c r="D152" s="11" t="n">
-        <v>2019</v>
+        <v>2004</v>
       </c>
       <c r="E152" s="14" t="inlineStr">
         <is>
@@ -13071,27 +13079,27 @@
       </c>
       <c r="I152" s="11" t="inlineStr">
         <is>
-          <t>10-50</t>
+          <t>1-10</t>
         </is>
       </c>
       <c r="J152" s="14" t="inlineStr">
         <is>
-          <t>Drone surveying; infrastructure asset mapping</t>
+          <t>Precision land surveying; geospatial drone mapping</t>
         </is>
       </c>
       <c r="K152" s="14" t="inlineStr">
         <is>
-          <t>Drone inspection and geospatial engineering data processing for infrastructure networks</t>
+          <t>Aerial infrastructure mapping and corridor survey analytics</t>
         </is>
       </c>
       <c r="L152" s="14" t="inlineStr">
         <is>
-          <t>DGPS ground data systems; photogrammetry UAV mapping modules; digital asset rendering suites</t>
+          <t>Precision mapping drones; geodetic DGPS receivers; aerial topography processing systems</t>
         </is>
       </c>
       <c r="M152" s="11" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Offline</t>
         </is>
       </c>
       <c r="N152" s="14" t="inlineStr"/>
@@ -13100,17 +13108,17 @@
       <c r="Q152" s="14" t="inlineStr"/>
       <c r="R152" s="14" t="inlineStr">
         <is>
-          <t>+91 98258 06532</t>
+          <t>+91 98250 41903</t>
         </is>
       </c>
       <c r="S152" s="13" t="inlineStr">
         <is>
-          <t>https://tessellateearthscan.com</t>
+          <t>https://aksharcon.com</t>
         </is>
       </c>
       <c r="T152" s="13" t="inlineStr">
         <is>
-          <t>krishna@tessellateearthscan.com</t>
+          <t>info@aksharcon.com</t>
         </is>
       </c>
       <c r="U152" s="11" t="inlineStr">
@@ -13119,22 +13127,22 @@
         </is>
       </c>
     </row>
-    <row r="153" ht="33" customHeight="1">
+    <row r="153" ht="46.5" customHeight="1">
       <c r="A153" s="15" t="n">
         <v>148</v>
       </c>
       <c r="B153" s="16" t="inlineStr">
         <is>
-          <t>Akshar Consultancy</t>
+          <t>SkyMapper Drones</t>
         </is>
       </c>
       <c r="C153" s="17" t="inlineStr">
         <is>
-          <t>https://aksharcon.com</t>
+          <t>skymapperdrones.com</t>
         </is>
       </c>
       <c r="D153" s="15" t="n">
-        <v>2004</v>
+        <v>2024</v>
       </c>
       <c r="E153" s="18" t="inlineStr">
         <is>
@@ -13153,7 +13161,7 @@
       </c>
       <c r="H153" s="18" t="inlineStr">
         <is>
-          <t>Private Company</t>
+          <t>Family-Owned</t>
         </is>
       </c>
       <c r="I153" s="15" t="inlineStr">
@@ -13163,17 +13171,17 @@
       </c>
       <c r="J153" s="18" t="inlineStr">
         <is>
-          <t>Precision land surveying; geospatial drone mapping</t>
+          <t>Geospatial aerial mapping and UAV tracking data inspection packages</t>
         </is>
       </c>
       <c r="K153" s="18" t="inlineStr">
         <is>
-          <t>Aerial infrastructure mapping and corridor survey analytics</t>
+          <t>Aerial asset logging and risk management evaluation for linear networks and utility setups</t>
         </is>
       </c>
       <c r="L153" s="18" t="inlineStr">
         <is>
-          <t>Precision mapping drones; geodetic DGPS receivers; aerial topography processing systems</t>
+          <t>High-resolution orthomosaic imagery, 3D city and utility boundary models, Geographic Information System (GIS) frameworks</t>
         </is>
       </c>
       <c r="M153" s="15" t="inlineStr">
@@ -13185,21 +13193,13 @@
       <c r="O153" s="18" t="inlineStr"/>
       <c r="P153" s="18" t="inlineStr"/>
       <c r="Q153" s="18" t="inlineStr"/>
-      <c r="R153" s="18" t="inlineStr">
-        <is>
-          <t>+91 98250 41903</t>
-        </is>
-      </c>
+      <c r="R153" s="18" t="inlineStr"/>
       <c r="S153" s="17" t="inlineStr">
         <is>
-          <t>https://aksharcon.com</t>
-        </is>
-      </c>
-      <c r="T153" s="17" t="inlineStr">
-        <is>
-          <t>info@aksharcon.com</t>
-        </is>
-      </c>
+          <t>skymapperdrones.com</t>
+        </is>
+      </c>
+      <c r="T153" s="18" t="inlineStr"/>
       <c r="U153" s="15" t="inlineStr">
         <is>
           <t>+91 / IN</t>
@@ -13212,16 +13212,16 @@
       </c>
       <c r="B154" s="12" t="inlineStr">
         <is>
-          <t>SkyMapper Drones</t>
+          <t>SkyRoot Technologies</t>
         </is>
       </c>
       <c r="C154" s="13" t="inlineStr">
         <is>
-          <t>skymapperdrones.com</t>
+          <t>skyroottechnologies.com</t>
         </is>
       </c>
       <c r="D154" s="11" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E154" s="14" t="inlineStr">
         <is>
@@ -13250,17 +13250,17 @@
       </c>
       <c r="J154" s="14" t="inlineStr">
         <is>
-          <t>Geospatial aerial mapping and UAV tracking data inspection packages</t>
+          <t>Commercial drone service operations and precision aerial surveying platforms</t>
         </is>
       </c>
       <c r="K154" s="14" t="inlineStr">
         <is>
-          <t>Aerial asset logging and risk management evaluation for linear networks and utility setups</t>
+          <t>Thermal mapping and spatial corridor auditing for industrial grid infrastructure installations</t>
         </is>
       </c>
       <c r="L154" s="14" t="inlineStr">
         <is>
-          <t>High-resolution orthomosaic imagery, 3D city and utility boundary models, Geographic Information System (GIS) frameworks</t>
+          <t>Radiometric thermal imaging systems, GIS map layering tools, Photogrammetric asset logging</t>
         </is>
       </c>
       <c r="M154" s="11" t="inlineStr">
@@ -13275,7 +13275,7 @@
       <c r="R154" s="14" t="inlineStr"/>
       <c r="S154" s="13" t="inlineStr">
         <is>
-          <t>skymapperdrones.com</t>
+          <t>skyroottechnologies.com</t>
         </is>
       </c>
       <c r="T154" s="14" t="inlineStr"/>
@@ -13291,20 +13291,20 @@
       </c>
       <c r="B155" s="16" t="inlineStr">
         <is>
-          <t>SkyRoot Technologies</t>
+          <t>VibMaster</t>
         </is>
       </c>
       <c r="C155" s="17" t="inlineStr">
         <is>
-          <t>skyroottechnologies.com</t>
+          <t>https://vibmaster.in/</t>
         </is>
       </c>
       <c r="D155" s="15" t="n">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="E155" s="18" t="inlineStr">
         <is>
-          <t>Ahmedabad, India</t>
+          <t>Surat, India</t>
         </is>
       </c>
       <c r="F155" s="18" t="inlineStr">
@@ -13319,27 +13319,27 @@
       </c>
       <c r="H155" s="18" t="inlineStr">
         <is>
-          <t>Family-Owned</t>
+          <t>Private Company</t>
         </is>
       </c>
       <c r="I155" s="15" t="inlineStr">
         <is>
-          <t>1-10</t>
+          <t>11-50</t>
         </is>
       </c>
       <c r="J155" s="18" t="inlineStr">
         <is>
-          <t>Commercial drone service operations and precision aerial surveying platforms</t>
+          <t>Condition monitoring services; NDT testing solutions</t>
         </is>
       </c>
       <c r="K155" s="18" t="inlineStr">
         <is>
-          <t>Thermal mapping and spatial corridor auditing for industrial grid infrastructure installations</t>
+          <t>Predictive maintenance, non-destructive testing, and thermographic field diagnostics for infrastructure utility systems</t>
         </is>
       </c>
       <c r="L155" s="18" t="inlineStr">
         <is>
-          <t>Radiometric thermal imaging systems, GIS map layering tools, Photogrammetric asset logging</t>
+          <t>Infrared thermography, robotic inspection crawlers, drone visual sensors</t>
         </is>
       </c>
       <c r="M155" s="15" t="inlineStr">
@@ -13347,17 +13347,37 @@
           <t>Offline</t>
         </is>
       </c>
-      <c r="N155" s="18" t="inlineStr"/>
-      <c r="O155" s="18" t="inlineStr"/>
-      <c r="P155" s="18" t="inlineStr"/>
+      <c r="N155" s="18" t="inlineStr">
+        <is>
+          <t>Urmila N Khadia</t>
+        </is>
+      </c>
+      <c r="O155" s="18" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="P155" s="17" t="inlineStr">
+        <is>
+          <t>info@vibmaster.in</t>
+        </is>
+      </c>
       <c r="Q155" s="18" t="inlineStr"/>
-      <c r="R155" s="18" t="inlineStr"/>
+      <c r="R155" s="18" t="inlineStr">
+        <is>
+          <t>+91 9081896255</t>
+        </is>
+      </c>
       <c r="S155" s="17" t="inlineStr">
         <is>
-          <t>skyroottechnologies.com</t>
-        </is>
-      </c>
-      <c r="T155" s="18" t="inlineStr"/>
+          <t>https://vibmaster.in/</t>
+        </is>
+      </c>
+      <c r="T155" s="17" t="inlineStr">
+        <is>
+          <t>info@vibmaster.in</t>
+        </is>
+      </c>
       <c r="U155" s="15" t="inlineStr">
         <is>
           <t>+91 / IN</t>
@@ -13370,20 +13390,20 @@
       </c>
       <c r="B156" s="12" t="inlineStr">
         <is>
-          <t>VibMaster</t>
+          <t>Suncad Technologies Pvt Ltd</t>
         </is>
       </c>
       <c r="C156" s="13" t="inlineStr">
         <is>
-          <t>https://vibmaster.in/</t>
+          <t>suncad.in</t>
         </is>
       </c>
       <c r="D156" s="11" t="n">
-        <v>2021</v>
+        <v>2012</v>
       </c>
       <c r="E156" s="14" t="inlineStr">
         <is>
-          <t>Surat, India</t>
+          <t>Ahmedabad, India</t>
         </is>
       </c>
       <c r="F156" s="14" t="inlineStr">
@@ -13408,17 +13428,17 @@
       </c>
       <c r="J156" s="14" t="inlineStr">
         <is>
-          <t>Condition monitoring services; NDT testing solutions</t>
+          <t>3D LiDAR scanning; utility data processing services</t>
         </is>
       </c>
       <c r="K156" s="14" t="inlineStr">
         <is>
-          <t>Predictive maintenance, non-destructive testing, and thermographic field diagnostics for infrastructure utility systems</t>
+          <t>Point cloud classification and utility asset data modeling</t>
         </is>
       </c>
       <c r="L156" s="14" t="inlineStr">
         <is>
-          <t>Infrared thermography, robotic inspection crawlers, drone visual sensors</t>
+          <t>Airborne LiDAR sensors, LAS binary point cloud formatting, and DEM/DTM generation software</t>
         </is>
       </c>
       <c r="M156" s="11" t="inlineStr">
@@ -13426,35 +13446,27 @@
           <t>Offline</t>
         </is>
       </c>
-      <c r="N156" s="14" t="inlineStr">
-        <is>
-          <t>Urmila N Khadia</t>
-        </is>
-      </c>
-      <c r="O156" s="14" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
+      <c r="N156" s="14" t="inlineStr"/>
+      <c r="O156" s="14" t="inlineStr"/>
       <c r="P156" s="13" t="inlineStr">
         <is>
-          <t>info@vibmaster.in</t>
+          <t>info@suncad.in</t>
         </is>
       </c>
       <c r="Q156" s="14" t="inlineStr"/>
       <c r="R156" s="14" t="inlineStr">
         <is>
-          <t>+91 9081896255</t>
+          <t>+919925023229</t>
         </is>
       </c>
       <c r="S156" s="13" t="inlineStr">
         <is>
-          <t>https://vibmaster.in/</t>
+          <t>suncad.in</t>
         </is>
       </c>
       <c r="T156" s="13" t="inlineStr">
         <is>
-          <t>info@vibmaster.in</t>
+          <t>info@suncad.in</t>
         </is>
       </c>
       <c r="U156" s="11" t="inlineStr">
@@ -13463,22 +13475,22 @@
         </is>
       </c>
     </row>
-    <row r="157" ht="46.5" customHeight="1">
+    <row r="157" ht="33" customHeight="1">
       <c r="A157" s="15" t="n">
         <v>152</v>
       </c>
       <c r="B157" s="16" t="inlineStr">
         <is>
-          <t>Suncad Technologies Pvt Ltd</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="C157" s="17" t="inlineStr">
         <is>
-          <t>suncad.in</t>
+          <t>flowerdroppingdrone.com</t>
         </is>
       </c>
       <c r="D157" s="15" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="E157" s="18" t="inlineStr">
         <is>
@@ -13502,52 +13514,52 @@
       </c>
       <c r="I157" s="15" t="inlineStr">
         <is>
-          <t>11-50</t>
+          <t>1-10</t>
         </is>
       </c>
       <c r="J157" s="18" t="inlineStr">
         <is>
-          <t>3D LiDAR scanning; utility data processing services</t>
+          <t>Customized UAVs; inspection robots</t>
         </is>
       </c>
       <c r="K157" s="18" t="inlineStr">
         <is>
-          <t>Point cloud classification and utility asset data modeling</t>
+          <t>Powerline installation and drone cable stringing operations</t>
         </is>
       </c>
       <c r="L157" s="18" t="inlineStr">
         <is>
-          <t>Airborne LiDAR sensors, LAS binary point cloud formatting, and DEM/DTM generation software</t>
+          <t>Hexacopter drone platforms, carbon fiber frames, and automated GPS navigation systems</t>
         </is>
       </c>
       <c r="M157" s="15" t="inlineStr">
         <is>
-          <t>Offline</t>
-        </is>
-      </c>
-      <c r="N157" s="18" t="inlineStr"/>
-      <c r="O157" s="18" t="inlineStr"/>
-      <c r="P157" s="17" t="inlineStr">
-        <is>
-          <t>info@suncad.in</t>
-        </is>
-      </c>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="N157" s="18" t="inlineStr">
+        <is>
+          <t>Umang Joshi</t>
+        </is>
+      </c>
+      <c r="O157" s="18" t="inlineStr">
+        <is>
+          <t>Proprietor</t>
+        </is>
+      </c>
+      <c r="P157" s="18" t="inlineStr"/>
       <c r="Q157" s="18" t="inlineStr"/>
       <c r="R157" s="18" t="inlineStr">
         <is>
-          <t>+919925023229</t>
+          <t>+918047630965</t>
         </is>
       </c>
       <c r="S157" s="17" t="inlineStr">
         <is>
-          <t>suncad.in</t>
-        </is>
-      </c>
-      <c r="T157" s="17" t="inlineStr">
-        <is>
-          <t>info@suncad.in</t>
-        </is>
-      </c>
+          <t>flowerdroppingdrone.com</t>
+        </is>
+      </c>
+      <c r="T157" s="18" t="inlineStr"/>
       <c r="U157" s="15" t="inlineStr">
         <is>
           <t>+91 / IN</t>
@@ -13560,20 +13572,20 @@
       </c>
       <c r="B158" s="12" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Global Services</t>
         </is>
       </c>
       <c r="C158" s="13" t="inlineStr">
         <is>
-          <t>flowerdroppingdrone.com</t>
+          <t>globalservice.co.in</t>
         </is>
       </c>
       <c r="D158" s="11" t="n">
-        <v>2011</v>
+        <v>2008</v>
       </c>
       <c r="E158" s="14" t="inlineStr">
         <is>
-          <t>Ahmedabad, India</t>
+          <t>Vadodara, India</t>
         </is>
       </c>
       <c r="F158" s="14" t="inlineStr">
@@ -13593,32 +13605,32 @@
       </c>
       <c r="I158" s="11" t="inlineStr">
         <is>
-          <t>1-10</t>
+          <t>26-50</t>
         </is>
       </c>
       <c r="J158" s="14" t="inlineStr">
         <is>
-          <t>Customized UAVs; inspection robots</t>
+          <t>Drone aerial surveys; geospatial data processing</t>
         </is>
       </c>
       <c r="K158" s="14" t="inlineStr">
         <is>
-          <t>Powerline installation and drone cable stringing operations</t>
+          <t>Power transmission line route verification and topographic corridor mapping</t>
         </is>
       </c>
       <c r="L158" s="14" t="inlineStr">
         <is>
-          <t>Hexacopter drone platforms, carbon fiber frames, and automated GPS navigation systems</t>
+          <t>DGPS receivers, UAV imaging cameras, and total station surveying equipment</t>
         </is>
       </c>
       <c r="M158" s="11" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Offline</t>
         </is>
       </c>
       <c r="N158" s="14" t="inlineStr">
         <is>
-          <t>Umang Joshi</t>
+          <t>Sudhir Manoharrav Shinde</t>
         </is>
       </c>
       <c r="O158" s="14" t="inlineStr">
@@ -13630,12 +13642,12 @@
       <c r="Q158" s="14" t="inlineStr"/>
       <c r="R158" s="14" t="inlineStr">
         <is>
-          <t>+918047630965</t>
+          <t>08047814557</t>
         </is>
       </c>
       <c r="S158" s="13" t="inlineStr">
         <is>
-          <t>flowerdroppingdrone.com</t>
+          <t>globalservice.co.in</t>
         </is>
       </c>
       <c r="T158" s="14" t="inlineStr"/>
@@ -13651,20 +13663,20 @@
       </c>
       <c r="B159" s="16" t="inlineStr">
         <is>
-          <t>Global Services</t>
+          <t>SRD Quality Services Pvt. Ltd.</t>
         </is>
       </c>
       <c r="C159" s="17" t="inlineStr">
         <is>
-          <t>globalservice.co.in</t>
+          <t>srdquality.com</t>
         </is>
       </c>
       <c r="D159" s="15" t="n">
-        <v>2008</v>
+        <v>2012</v>
       </c>
       <c r="E159" s="18" t="inlineStr">
         <is>
-          <t>Vadodara, India</t>
+          <t>Rajkot, India</t>
         </is>
       </c>
       <c r="F159" s="18" t="inlineStr">
@@ -13684,22 +13696,22 @@
       </c>
       <c r="I159" s="15" t="inlineStr">
         <is>
-          <t>26-50</t>
+          <t>11-50</t>
         </is>
       </c>
       <c r="J159" s="18" t="inlineStr">
         <is>
-          <t>Drone aerial surveys; geospatial data processing</t>
+          <t>Third-party inspection services; project management consultancy</t>
         </is>
       </c>
       <c r="K159" s="18" t="inlineStr">
         <is>
-          <t>Power transmission line route verification and topographic corridor mapping</t>
+          <t>Drone survey and design consultancy for public infrastructure and utilities</t>
         </is>
       </c>
       <c r="L159" s="18" t="inlineStr">
         <is>
-          <t>DGPS receivers, UAV imaging cameras, and total station surveying equipment</t>
+          <t>UAV aerial mapping cameras, GIS database management, and 3D modeling tools</t>
         </is>
       </c>
       <c r="M159" s="15" t="inlineStr">
@@ -13707,55 +13719,51 @@
           <t>Offline</t>
         </is>
       </c>
-      <c r="N159" s="18" t="inlineStr">
-        <is>
-          <t>Sudhir Manoharrav Shinde</t>
-        </is>
-      </c>
-      <c r="O159" s="18" t="inlineStr">
-        <is>
-          <t>Proprietor</t>
-        </is>
-      </c>
-      <c r="P159" s="18" t="inlineStr"/>
+      <c r="N159" s="18" t="inlineStr"/>
+      <c r="O159" s="18" t="inlineStr"/>
+      <c r="P159" s="17" t="inlineStr">
+        <is>
+          <t>srd198@yahoo.com</t>
+        </is>
+      </c>
       <c r="Q159" s="18" t="inlineStr"/>
-      <c r="R159" s="18" t="inlineStr">
-        <is>
-          <t>08047814557</t>
-        </is>
-      </c>
+      <c r="R159" s="18" t="inlineStr"/>
       <c r="S159" s="17" t="inlineStr">
         <is>
-          <t>globalservice.co.in</t>
-        </is>
-      </c>
-      <c r="T159" s="18" t="inlineStr"/>
+          <t>srdquality.com</t>
+        </is>
+      </c>
+      <c r="T159" s="17" t="inlineStr">
+        <is>
+          <t>srd198@yahoo.com</t>
+        </is>
+      </c>
       <c r="U159" s="15" t="inlineStr">
         <is>
           <t>+91 / IN</t>
         </is>
       </c>
     </row>
-    <row r="160" ht="33" customHeight="1">
+    <row r="160" ht="73.5" customHeight="1">
       <c r="A160" s="11" t="n">
         <v>155</v>
       </c>
       <c r="B160" s="12" t="inlineStr">
         <is>
-          <t>SRD Quality Services Pvt. Ltd.</t>
+          <t>Jainam Engineering</t>
         </is>
       </c>
       <c r="C160" s="13" t="inlineStr">
         <is>
-          <t>srdquality.com</t>
+          <t>https://www.justdial.com/Ahmedabad/Jainam-Engineering-Opposite-Jain-Derasar-Above-Syndicate-Bank-Bhimjipura/079PXX79-XX79-130328194514-L4H5_BZDET</t>
         </is>
       </c>
       <c r="D160" s="11" t="n">
-        <v>2012</v>
+        <v>2007</v>
       </c>
       <c r="E160" s="14" t="inlineStr">
         <is>
-          <t>Rajkot, India</t>
+          <t>Ahmedabad, India</t>
         </is>
       </c>
       <c r="F160" s="14" t="inlineStr">
@@ -13775,22 +13783,22 @@
       </c>
       <c r="I160" s="11" t="inlineStr">
         <is>
-          <t>11-50</t>
+          <t>10-50</t>
         </is>
       </c>
       <c r="J160" s="14" t="inlineStr">
         <is>
-          <t>Third-party inspection services; project management consultancy</t>
+          <t>Engineering land surveys; Total station infrastructure validation</t>
         </is>
       </c>
       <c r="K160" s="14" t="inlineStr">
         <is>
-          <t>Drone survey and design consultancy for public infrastructure and utilities</t>
+          <t>Railway asset monitoring and high-voltage transmission route delineation</t>
         </is>
       </c>
       <c r="L160" s="14" t="inlineStr">
         <is>
-          <t>UAV aerial mapping cameras, GIS database management, and 3D modeling tools</t>
+          <t>Drone photogrammetry networks, GNSS/RTK hardware</t>
         </is>
       </c>
       <c r="M160" s="11" t="inlineStr">
@@ -13800,49 +13808,41 @@
       </c>
       <c r="N160" s="14" t="inlineStr"/>
       <c r="O160" s="14" t="inlineStr"/>
-      <c r="P160" s="13" t="inlineStr">
-        <is>
-          <t>srd198@yahoo.com</t>
-        </is>
-      </c>
+      <c r="P160" s="14" t="inlineStr"/>
       <c r="Q160" s="14" t="inlineStr"/>
       <c r="R160" s="14" t="inlineStr"/>
       <c r="S160" s="13" t="inlineStr">
         <is>
-          <t>srdquality.com</t>
-        </is>
-      </c>
-      <c r="T160" s="13" t="inlineStr">
-        <is>
-          <t>srd198@yahoo.com</t>
-        </is>
-      </c>
+          <t>https://www.justdial.com/Ahmedabad/Jainam-Engineering-Opposite-Jain-Derasar-Above-Syndicate-Bank-Bhimjipura/079PXX79-XX79-130328194514-L4H5_BZDET</t>
+        </is>
+      </c>
+      <c r="T160" s="14" t="inlineStr"/>
       <c r="U160" s="11" t="inlineStr">
         <is>
           <t>+91 / IN</t>
         </is>
       </c>
     </row>
-    <row r="161" ht="73.5" customHeight="1">
+    <row r="161" ht="33" customHeight="1">
       <c r="A161" s="15" t="n">
         <v>156</v>
       </c>
       <c r="B161" s="16" t="inlineStr">
         <is>
-          <t>Jainam Engineering</t>
+          <t>Theodesh Consultants</t>
         </is>
       </c>
       <c r="C161" s="17" t="inlineStr">
         <is>
-          <t>https://www.justdial.com/Ahmedabad/Jainam-Engineering-Opposite-Jain-Derasar-Above-Syndicate-Bank-Bhimjipura/079PXX79-XX79-130328194514-L4H5_BZDET</t>
+          <t>tdcl.in</t>
         </is>
       </c>
       <c r="D161" s="15" t="n">
-        <v>2007</v>
+        <v>2001</v>
       </c>
       <c r="E161" s="18" t="inlineStr">
         <is>
-          <t>Ahmedabad, India</t>
+          <t>Vadodara, India</t>
         </is>
       </c>
       <c r="F161" s="18" t="inlineStr">
@@ -13862,22 +13862,22 @@
       </c>
       <c r="I161" s="15" t="inlineStr">
         <is>
-          <t>10-50</t>
+          <t>11-50</t>
         </is>
       </c>
       <c r="J161" s="18" t="inlineStr">
         <is>
-          <t>Engineering land surveys; Total station infrastructure validation</t>
+          <t>Geospatial GIS engineering; Pipeline and asset corridor surveys</t>
         </is>
       </c>
       <c r="K161" s="18" t="inlineStr">
         <is>
-          <t>Railway asset monitoring and high-voltage transmission route delineation</t>
+          <t>Large-scale utility corridor mapping and geospatial model integration.</t>
         </is>
       </c>
       <c r="L161" s="18" t="inlineStr">
         <is>
-          <t>Drone photogrammetry networks, GNSS/RTK hardware</t>
+          <t>Drone-mounted LiDAR systems and custom spatial database modules.</t>
         </is>
       </c>
       <c r="M161" s="15" t="inlineStr">
@@ -13892,10 +13892,14 @@
       <c r="R161" s="18" t="inlineStr"/>
       <c r="S161" s="17" t="inlineStr">
         <is>
-          <t>https://www.justdial.com/Ahmedabad/Jainam-Engineering-Opposite-Jain-Derasar-Above-Syndicate-Bank-Bhimjipura/079PXX79-XX79-130328194514-L4H5_BZDET</t>
-        </is>
-      </c>
-      <c r="T161" s="18" t="inlineStr"/>
+          <t>tdcl.in</t>
+        </is>
+      </c>
+      <c r="T161" s="17" t="inlineStr">
+        <is>
+          <t>theodesh@tdcl.in</t>
+        </is>
+      </c>
       <c r="U161" s="15" t="inlineStr">
         <is>
           <t>+91 / IN</t>
@@ -13908,20 +13912,20 @@
       </c>
       <c r="B162" s="12" t="inlineStr">
         <is>
-          <t>Theodesh Consultants</t>
+          <t>X-way Enterprise Engineers &amp; Surveyors</t>
         </is>
       </c>
       <c r="C162" s="13" t="inlineStr">
         <is>
-          <t>tdcl.in</t>
+          <t>http://xwayenterprisesurvey.in</t>
         </is>
       </c>
       <c r="D162" s="11" t="n">
-        <v>2001</v>
+        <v>2006</v>
       </c>
       <c r="E162" s="14" t="inlineStr">
         <is>
-          <t>Vadodara, India</t>
+          <t>Rajkot, India</t>
         </is>
       </c>
       <c r="F162" s="14" t="inlineStr">
@@ -13941,22 +13945,22 @@
       </c>
       <c r="I162" s="11" t="inlineStr">
         <is>
-          <t>11-50</t>
+          <t>10-50</t>
         </is>
       </c>
       <c r="J162" s="14" t="inlineStr">
         <is>
-          <t>Geospatial GIS engineering; Pipeline and asset corridor surveys</t>
+          <t>DGPS control mapping; Engineering land inspection services</t>
         </is>
       </c>
       <c r="K162" s="14" t="inlineStr">
         <is>
-          <t>Large-scale utility corridor mapping and geospatial model integration.</t>
+          <t>High-accuracy topographic drone layouts and asset corridor validation scans.</t>
         </is>
       </c>
       <c r="L162" s="14" t="inlineStr">
         <is>
-          <t>Drone-mounted LiDAR systems and custom spatial database modules.</t>
+          <t>UAV drone cameras and advanced georeferencing coordinate systems.</t>
         </is>
       </c>
       <c r="M162" s="11" t="inlineStr">
@@ -13971,40 +13975,36 @@
       <c r="R162" s="14" t="inlineStr"/>
       <c r="S162" s="13" t="inlineStr">
         <is>
-          <t>tdcl.in</t>
-        </is>
-      </c>
-      <c r="T162" s="13" t="inlineStr">
-        <is>
-          <t>theodesh@tdcl.in</t>
-        </is>
-      </c>
+          <t>http://xwayenterprisesurvey.in</t>
+        </is>
+      </c>
+      <c r="T162" s="14" t="inlineStr"/>
       <c r="U162" s="11" t="inlineStr">
         <is>
           <t>+91 / IN</t>
         </is>
       </c>
     </row>
-    <row r="163" ht="33" customHeight="1">
+    <row r="163" ht="60" customHeight="1">
       <c r="A163" s="15" t="n">
         <v>158</v>
       </c>
       <c r="B163" s="16" t="inlineStr">
         <is>
-          <t>X-way Enterprise Engineers &amp; Surveyors</t>
+          <t>Elegrow Technology</t>
         </is>
       </c>
       <c r="C163" s="17" t="inlineStr">
         <is>
-          <t>http://xwayenterprisesurvey.in</t>
+          <t>https://elegrow.com</t>
         </is>
       </c>
       <c r="D163" s="15" t="n">
-        <v>2006</v>
+        <v>2012</v>
       </c>
       <c r="E163" s="18" t="inlineStr">
         <is>
-          <t>Rajkot, India</t>
+          <t>Surat, India</t>
         </is>
       </c>
       <c r="F163" s="18" t="inlineStr">
@@ -14024,66 +14024,74 @@
       </c>
       <c r="I163" s="15" t="inlineStr">
         <is>
-          <t>10-50</t>
+          <t>11-50</t>
         </is>
       </c>
       <c r="J163" s="18" t="inlineStr">
         <is>
-          <t>DGPS control mapping; Engineering land inspection services</t>
+          <t>Power system engineering; industrial asset thermography and aerial mapping</t>
         </is>
       </c>
       <c r="K163" s="18" t="inlineStr">
         <is>
-          <t>High-accuracy topographic drone layouts and asset corridor validation scans.</t>
+          <t>Predictive and preventive asset maintenance including drone-based high-definition image capturing of telecommunication and power lines.</t>
         </is>
       </c>
       <c r="L163" s="18" t="inlineStr">
         <is>
-          <t>UAV drone cameras and advanced georeferencing coordinate systems.</t>
+          <t>Robotic cleaning solutions, drone thermography mapping, electrical asset condition analytics</t>
         </is>
       </c>
       <c r="M163" s="15" t="inlineStr">
         <is>
-          <t>Offline</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="N163" s="18" t="inlineStr"/>
       <c r="O163" s="18" t="inlineStr"/>
       <c r="P163" s="18" t="inlineStr"/>
       <c r="Q163" s="18" t="inlineStr"/>
-      <c r="R163" s="18" t="inlineStr"/>
+      <c r="R163" s="18" t="inlineStr">
+        <is>
+          <t>+91 99797 00577</t>
+        </is>
+      </c>
       <c r="S163" s="17" t="inlineStr">
         <is>
-          <t>http://xwayenterprisesurvey.in</t>
-        </is>
-      </c>
-      <c r="T163" s="18" t="inlineStr"/>
+          <t>https://elegrow.com</t>
+        </is>
+      </c>
+      <c r="T163" s="17" t="inlineStr">
+        <is>
+          <t>info@elegrow.com</t>
+        </is>
+      </c>
       <c r="U163" s="15" t="inlineStr">
         <is>
           <t>+91 / IN</t>
         </is>
       </c>
     </row>
-    <row r="164" ht="60" customHeight="1">
+    <row r="164" ht="46.5" customHeight="1">
       <c r="A164" s="11" t="n">
         <v>159</v>
       </c>
       <c r="B164" s="12" t="inlineStr">
         <is>
-          <t>Elegrow Technology</t>
+          <t>Digital Edge</t>
         </is>
       </c>
       <c r="C164" s="13" t="inlineStr">
         <is>
-          <t>https://elegrow.com</t>
+          <t>https://digitaledge.net.in</t>
         </is>
       </c>
       <c r="D164" s="11" t="n">
-        <v>2012</v>
+        <v>2021</v>
       </c>
       <c r="E164" s="14" t="inlineStr">
         <is>
-          <t>Surat, India</t>
+          <t>Vadodara, India</t>
         </is>
       </c>
       <c r="F164" s="14" t="inlineStr">
@@ -14103,22 +14111,22 @@
       </c>
       <c r="I164" s="11" t="inlineStr">
         <is>
-          <t>11-50</t>
+          <t>1-10</t>
         </is>
       </c>
       <c r="J164" s="14" t="inlineStr">
         <is>
-          <t>Power system engineering; industrial asset thermography and aerial mapping</t>
+          <t>Industrial EHS management software; drone-backed technical asset inspections</t>
         </is>
       </c>
       <c r="K164" s="14" t="inlineStr">
         <is>
-          <t>Predictive and preventive asset maintenance including drone-based high-definition image capturing of telecommunication and power lines.</t>
+          <t>Safe, contactless aerial diagnostics of dangerous confined spaces and active high-voltage utility components.</t>
         </is>
       </c>
       <c r="L164" s="14" t="inlineStr">
         <is>
-          <t>Robotic cleaning solutions, drone thermography mapping, electrical asset condition analytics</t>
+          <t>High-resolution thermal sensors, specialized UAV inspection payloads, EHS parameter timers</t>
         </is>
       </c>
       <c r="M164" s="11" t="inlineStr">
@@ -14126,23 +14134,35 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="N164" s="14" t="inlineStr"/>
-      <c r="O164" s="14" t="inlineStr"/>
-      <c r="P164" s="14" t="inlineStr"/>
+      <c r="N164" s="14" t="inlineStr">
+        <is>
+          <t>Udayan Modhe</t>
+        </is>
+      </c>
+      <c r="O164" s="14" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="P164" s="13" t="inlineStr">
+        <is>
+          <t>udayan@digitaledge.net.in</t>
+        </is>
+      </c>
       <c r="Q164" s="14" t="inlineStr"/>
       <c r="R164" s="14" t="inlineStr">
         <is>
-          <t>+91 99797 00577</t>
+          <t>+91 95372 19666</t>
         </is>
       </c>
       <c r="S164" s="13" t="inlineStr">
         <is>
-          <t>https://elegrow.com</t>
+          <t>https://digitaledge.net.in</t>
         </is>
       </c>
       <c r="T164" s="13" t="inlineStr">
         <is>
-          <t>info@elegrow.com</t>
+          <t>info@digitaledge.net.in</t>
         </is>
       </c>
       <c r="U164" s="11" t="inlineStr">
@@ -14157,20 +14177,20 @@
       </c>
       <c r="B165" s="16" t="inlineStr">
         <is>
-          <t>Digital Edge</t>
+          <t>Pruthvi Co-Ordinates</t>
         </is>
       </c>
       <c r="C165" s="17" t="inlineStr">
         <is>
-          <t>https://digitaledge.net.in</t>
+          <t>https://www.pruthvisurvey.in</t>
         </is>
       </c>
       <c r="D165" s="15" t="n">
-        <v>2021</v>
+        <v>1993</v>
       </c>
       <c r="E165" s="18" t="inlineStr">
         <is>
-          <t>Vadodara, India</t>
+          <t>Rajkot, India</t>
         </is>
       </c>
       <c r="F165" s="18" t="inlineStr">
@@ -14195,53 +14215,53 @@
       </c>
       <c r="J165" s="18" t="inlineStr">
         <is>
-          <t>Industrial EHS management software; drone-backed technical asset inspections</t>
+          <t>Topographical mapping; utility infrastructure land survey solutions</t>
         </is>
       </c>
       <c r="K165" s="18" t="inlineStr">
         <is>
-          <t>Safe, contactless aerial diagnostics of dangerous confined spaces and active high-voltage utility components.</t>
+          <t>Establishing highly precise control benchmarks for large-scale solar park grids and utility corridors.</t>
         </is>
       </c>
       <c r="L165" s="18" t="inlineStr">
         <is>
-          <t>High-resolution thermal sensors, specialized UAV inspection payloads, EHS parameter timers</t>
+          <t>Drone aerial photogrammetry software, DGPS coordinate georeferencing workflows</t>
         </is>
       </c>
       <c r="M165" s="15" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Offline</t>
         </is>
       </c>
       <c r="N165" s="18" t="inlineStr">
         <is>
-          <t>Udayan Modhe</t>
+          <t>Vinay Joshi</t>
         </is>
       </c>
       <c r="O165" s="18" t="inlineStr">
         <is>
-          <t>Founder</t>
+          <t>Lead Surveyor</t>
         </is>
       </c>
       <c r="P165" s="17" t="inlineStr">
         <is>
-          <t>udayan@digitaledge.net.in</t>
+          <t>pruthvinay@gmail.com</t>
         </is>
       </c>
       <c r="Q165" s="18" t="inlineStr"/>
       <c r="R165" s="18" t="inlineStr">
         <is>
-          <t>+91 95372 19666</t>
+          <t>+91 98252 40894</t>
         </is>
       </c>
       <c r="S165" s="17" t="inlineStr">
         <is>
-          <t>https://digitaledge.net.in</t>
+          <t>https://www.pruthvisurvey.in</t>
         </is>
       </c>
       <c r="T165" s="17" t="inlineStr">
         <is>
-          <t>info@digitaledge.net.in</t>
+          <t>info@pruthvisurvey.com</t>
         </is>
       </c>
       <c r="U165" s="15" t="inlineStr">
@@ -14250,26 +14270,26 @@
         </is>
       </c>
     </row>
-    <row r="166" ht="46.5" customHeight="1">
+    <row r="166" ht="33" customHeight="1">
       <c r="A166" s="11" t="n">
         <v>161</v>
       </c>
       <c r="B166" s="12" t="inlineStr">
         <is>
-          <t>Pruthvi Co-Ordinates</t>
+          <t>Rapidex Solutions</t>
         </is>
       </c>
       <c r="C166" s="13" t="inlineStr">
         <is>
-          <t>https://www.pruthvisurvey.in</t>
+          <t>http://rapidexsolutions.com</t>
         </is>
       </c>
       <c r="D166" s="11" t="n">
-        <v>1993</v>
+        <v>2019</v>
       </c>
       <c r="E166" s="14" t="inlineStr">
         <is>
-          <t>Rajkot, India</t>
+          <t>Ahmedabad, India</t>
         </is>
       </c>
       <c r="F166" s="14" t="inlineStr">
@@ -14294,77 +14314,57 @@
       </c>
       <c r="J166" s="14" t="inlineStr">
         <is>
-          <t>Topographical mapping; utility infrastructure land survey solutions</t>
+          <t>Transmission line mapping; substation and asset inspection</t>
         </is>
       </c>
       <c r="K166" s="14" t="inlineStr">
         <is>
-          <t>Establishing highly precise control benchmarks for large-scale solar park grids and utility corridors.</t>
+          <t>Combining traditional land surveying workflows with utility drone imagery and analysis</t>
         </is>
       </c>
       <c r="L166" s="14" t="inlineStr">
         <is>
-          <t>Drone aerial photogrammetry software, DGPS coordinate georeferencing workflows</t>
+          <t>UAV systems with thermal and HD payloads, GIS photogrammetry data tools</t>
         </is>
       </c>
       <c r="M166" s="11" t="inlineStr">
         <is>
-          <t>Offline</t>
-        </is>
-      </c>
-      <c r="N166" s="14" t="inlineStr">
-        <is>
-          <t>Vinay Joshi</t>
-        </is>
-      </c>
-      <c r="O166" s="14" t="inlineStr">
-        <is>
-          <t>Lead Surveyor</t>
-        </is>
-      </c>
-      <c r="P166" s="13" t="inlineStr">
-        <is>
-          <t>pruthvinay@gmail.com</t>
-        </is>
-      </c>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="N166" s="14" t="inlineStr"/>
+      <c r="O166" s="14" t="inlineStr"/>
+      <c r="P166" s="14" t="inlineStr"/>
       <c r="Q166" s="14" t="inlineStr"/>
-      <c r="R166" s="14" t="inlineStr">
-        <is>
-          <t>+91 98252 40894</t>
-        </is>
-      </c>
+      <c r="R166" s="14" t="inlineStr"/>
       <c r="S166" s="13" t="inlineStr">
         <is>
-          <t>https://www.pruthvisurvey.in</t>
-        </is>
-      </c>
-      <c r="T166" s="13" t="inlineStr">
-        <is>
-          <t>info@pruthvisurvey.com</t>
-        </is>
-      </c>
+          <t>http://rapidexsolutions.com</t>
+        </is>
+      </c>
+      <c r="T166" s="14" t="inlineStr"/>
       <c r="U166" s="11" t="inlineStr">
         <is>
           <t>+91 / IN</t>
         </is>
       </c>
     </row>
-    <row r="167" ht="33" customHeight="1">
+    <row r="167" ht="46.5" customHeight="1">
       <c r="A167" s="15" t="n">
         <v>162</v>
       </c>
       <c r="B167" s="16" t="inlineStr">
         <is>
-          <t>Rapidex Solutions</t>
+          <t>AV Aerials Drone Services</t>
         </is>
       </c>
       <c r="C167" s="17" t="inlineStr">
         <is>
-          <t>http://rapidexsolutions.com</t>
+          <t>https://avaerials.com</t>
         </is>
       </c>
       <c r="D167" s="15" t="n">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="E167" s="18" t="inlineStr">
         <is>
@@ -14393,17 +14393,17 @@
       </c>
       <c r="J167" s="18" t="inlineStr">
         <is>
-          <t>Transmission line mapping; substation and asset inspection</t>
+          <t>Aerial asset inspection; high-precision mapping and tracking</t>
         </is>
       </c>
       <c r="K167" s="18" t="inlineStr">
         <is>
-          <t>Combining traditional land surveying workflows with utility drone imagery and analysis</t>
+          <t>Delivering high-resolution site mapping and virtual 360 monitoring for infrastructure networks</t>
         </is>
       </c>
       <c r="L167" s="18" t="inlineStr">
         <is>
-          <t>UAV systems with thermal and HD payloads, GIS photogrammetry data tools</t>
+          <t>Commercial drone fleet, 4K digital imaging payloads, photogrammetry tools</t>
         </is>
       </c>
       <c r="M167" s="15" t="inlineStr">
@@ -14418,7 +14418,7 @@
       <c r="R167" s="18" t="inlineStr"/>
       <c r="S167" s="17" t="inlineStr">
         <is>
-          <t>http://rapidexsolutions.com</t>
+          <t>https://avaerials.com</t>
         </is>
       </c>
       <c r="T167" s="18" t="inlineStr"/>
@@ -14434,20 +14434,20 @@
       </c>
       <c r="B168" s="12" t="inlineStr">
         <is>
-          <t>AV Aerials Drone Services</t>
+          <t>Naksha Solutions</t>
         </is>
       </c>
       <c r="C168" s="13" t="inlineStr">
         <is>
-          <t>https://avaerials.com</t>
+          <t>https://naksha-solutions.com</t>
         </is>
       </c>
       <c r="D168" s="11" t="n">
-        <v>2022</v>
+        <v>2010</v>
       </c>
       <c r="E168" s="14" t="inlineStr">
         <is>
-          <t>Ahmedabad, India</t>
+          <t>Vadodara, India</t>
         </is>
       </c>
       <c r="F168" s="14" t="inlineStr">
@@ -14467,22 +14467,22 @@
       </c>
       <c r="I168" s="11" t="inlineStr">
         <is>
-          <t>1-10</t>
+          <t>11-50</t>
         </is>
       </c>
       <c r="J168" s="14" t="inlineStr">
         <is>
-          <t>Aerial asset inspection; high-precision mapping and tracking</t>
+          <t>Geospatial mapping services; aerial drone surveying; subsurface utility scanning</t>
         </is>
       </c>
       <c r="K168" s="14" t="inlineStr">
         <is>
-          <t>Delivering high-resolution site mapping and virtual 360 monitoring for infrastructure networks</t>
+          <t>Renewable energy site assessments and underground utility locating.</t>
         </is>
       </c>
       <c r="L168" s="14" t="inlineStr">
         <is>
-          <t>Commercial drone fleet, 4K digital imaging payloads, photogrammetry tools</t>
+          <t>LiDAR drone sensors, Ground Penetrating Radar (GPR) systems.</t>
         </is>
       </c>
       <c r="M168" s="11" t="inlineStr">
@@ -14494,13 +14494,21 @@
       <c r="O168" s="14" t="inlineStr"/>
       <c r="P168" s="14" t="inlineStr"/>
       <c r="Q168" s="14" t="inlineStr"/>
-      <c r="R168" s="14" t="inlineStr"/>
+      <c r="R168" s="14" t="inlineStr">
+        <is>
+          <t>+91 763 288 288 7</t>
+        </is>
+      </c>
       <c r="S168" s="13" t="inlineStr">
         <is>
-          <t>https://avaerials.com</t>
-        </is>
-      </c>
-      <c r="T168" s="14" t="inlineStr"/>
+          <t>https://naksha-solutions.com</t>
+        </is>
+      </c>
+      <c r="T168" s="13" t="inlineStr">
+        <is>
+          <t>info@naksha-solutions.com</t>
+        </is>
+      </c>
       <c r="U168" s="11" t="inlineStr">
         <is>
           <t>+91 / IN</t>
@@ -14513,12 +14521,12 @@
       </c>
       <c r="B169" s="16" t="inlineStr">
         <is>
-          <t>Naksha Solutions</t>
+          <t>DH Geo Consultancy</t>
         </is>
       </c>
       <c r="C169" s="17" t="inlineStr">
         <is>
-          <t>https://naksha-solutions.com</t>
+          <t>https://dhgeoconsultancy.com</t>
         </is>
       </c>
       <c r="D169" s="15" t="n">
@@ -14526,7 +14534,7 @@
       </c>
       <c r="E169" s="18" t="inlineStr">
         <is>
-          <t>Vadodara, India</t>
+          <t>Ahmedabad, India</t>
         </is>
       </c>
       <c r="F169" s="18" t="inlineStr">
@@ -14551,17 +14559,17 @@
       </c>
       <c r="J169" s="18" t="inlineStr">
         <is>
-          <t>Geospatial mapping services; aerial drone surveying; subsurface utility scanning</t>
+          <t>LiDAR topographic surveys; forest GIS mapping; geological consultancy</t>
         </is>
       </c>
       <c r="K169" s="18" t="inlineStr">
         <is>
-          <t>Renewable energy site assessments and underground utility locating.</t>
+          <t>Forest canopy analysis, vegetation encroachment detection, and sub-meter boundary demarcation.</t>
         </is>
       </c>
       <c r="L169" s="18" t="inlineStr">
         <is>
-          <t>LiDAR drone sensors, Ground Penetrating Radar (GPR) systems.</t>
+          <t>Drone-mounted LiDAR scanning systems, professional DGPS receivers.</t>
         </is>
       </c>
       <c r="M169" s="15" t="inlineStr">
@@ -14569,23 +14577,31 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="N169" s="18" t="inlineStr"/>
-      <c r="O169" s="18" t="inlineStr"/>
+      <c r="N169" s="18" t="inlineStr">
+        <is>
+          <t>Hardik Patel</t>
+        </is>
+      </c>
+      <c r="O169" s="18" t="inlineStr">
+        <is>
+          <t>Proprietor</t>
+        </is>
+      </c>
       <c r="P169" s="18" t="inlineStr"/>
       <c r="Q169" s="18" t="inlineStr"/>
       <c r="R169" s="18" t="inlineStr">
         <is>
-          <t>+91 763 288 288 7</t>
+          <t>+91 98259 26791</t>
         </is>
       </c>
       <c r="S169" s="17" t="inlineStr">
         <is>
-          <t>https://naksha-solutions.com</t>
+          <t>https://dhgeoconsultancy.com</t>
         </is>
       </c>
       <c r="T169" s="17" t="inlineStr">
         <is>
-          <t>info@naksha-solutions.com</t>
+          <t>dhgeoco@gmail.com</t>
         </is>
       </c>
       <c r="U169" s="15" t="inlineStr">
@@ -14594,26 +14610,26 @@
         </is>
       </c>
     </row>
-    <row r="170" ht="46.5" customHeight="1">
+    <row r="170" ht="33" customHeight="1">
       <c r="A170" s="11" t="n">
         <v>165</v>
       </c>
       <c r="B170" s="12" t="inlineStr">
         <is>
-          <t>DH Geo Consultancy</t>
+          <t>DIGITAL BIRD DRONES</t>
         </is>
       </c>
       <c r="C170" s="13" t="inlineStr">
         <is>
-          <t>https://dhgeoconsultancy.com</t>
+          <t>digitalbirddrones.com</t>
         </is>
       </c>
       <c r="D170" s="11" t="n">
-        <v>2010</v>
+        <v>2020</v>
       </c>
       <c r="E170" s="14" t="inlineStr">
         <is>
-          <t>Ahmedabad, India</t>
+          <t>Vadodara, India</t>
         </is>
       </c>
       <c r="F170" s="14" t="inlineStr">
@@ -14633,22 +14649,22 @@
       </c>
       <c r="I170" s="11" t="inlineStr">
         <is>
-          <t>11-50</t>
+          <t>1-10</t>
         </is>
       </c>
       <c r="J170" s="14" t="inlineStr">
         <is>
-          <t>LiDAR topographic surveys; forest GIS mapping; geological consultancy</t>
+          <t>Aerial mapping; Solar panel thermal inspection</t>
         </is>
       </c>
       <c r="K170" s="14" t="inlineStr">
         <is>
-          <t>Forest canopy analysis, vegetation encroachment detection, and sub-meter boundary demarcation.</t>
+          <t>UAV corridor mapping and solar utility analytics</t>
         </is>
       </c>
       <c r="L170" s="14" t="inlineStr">
         <is>
-          <t>Drone-mounted LiDAR scanning systems, professional DGPS receivers.</t>
+          <t>Thermal payload sensors; Aerial photogrammetry analytics</t>
         </is>
       </c>
       <c r="M170" s="11" t="inlineStr">
@@ -14656,33 +14672,21 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="N170" s="14" t="inlineStr">
-        <is>
-          <t>Hardik Patel</t>
-        </is>
-      </c>
-      <c r="O170" s="14" t="inlineStr">
-        <is>
-          <t>Proprietor</t>
-        </is>
-      </c>
+      <c r="N170" s="14" t="inlineStr"/>
+      <c r="O170" s="14" t="inlineStr"/>
       <c r="P170" s="14" t="inlineStr"/>
       <c r="Q170" s="14" t="inlineStr"/>
       <c r="R170" s="14" t="inlineStr">
         <is>
-          <t>+91 98259 26791</t>
+          <t>+91 78744 00918</t>
         </is>
       </c>
       <c r="S170" s="13" t="inlineStr">
         <is>
-          <t>https://dhgeoconsultancy.com</t>
-        </is>
-      </c>
-      <c r="T170" s="13" t="inlineStr">
-        <is>
-          <t>dhgeoco@gmail.com</t>
-        </is>
-      </c>
+          <t>digitalbirddrones.com</t>
+        </is>
+      </c>
+      <c r="T170" s="14" t="inlineStr"/>
       <c r="U170" s="11" t="inlineStr">
         <is>
           <t>+91 / IN</t>
@@ -14695,20 +14699,20 @@
       </c>
       <c r="B171" s="16" t="inlineStr">
         <is>
-          <t>DIGITAL BIRD DRONES</t>
+          <t>HRP Infra Pvt. Ltd.</t>
         </is>
       </c>
       <c r="C171" s="17" t="inlineStr">
         <is>
-          <t>digitalbirddrones.com</t>
+          <t>https://hrpinfra.com</t>
         </is>
       </c>
       <c r="D171" s="15" t="n">
-        <v>2020</v>
+        <v>2016</v>
       </c>
       <c r="E171" s="18" t="inlineStr">
         <is>
-          <t>Vadodara, India</t>
+          <t>Ahmedabad, India</t>
         </is>
       </c>
       <c r="F171" s="18" t="inlineStr">
@@ -14728,22 +14732,22 @@
       </c>
       <c r="I171" s="15" t="inlineStr">
         <is>
-          <t>1-10</t>
+          <t>20-100</t>
         </is>
       </c>
       <c r="J171" s="18" t="inlineStr">
         <is>
-          <t>Aerial mapping; Solar panel thermal inspection</t>
+          <t>Infrastructure consulting; GIS mapping services</t>
         </is>
       </c>
       <c r="K171" s="18" t="inlineStr">
         <is>
-          <t>UAV corridor mapping and solar utility analytics</t>
+          <t>Urban infrastructure and utility asset mapping layout analysis</t>
         </is>
       </c>
       <c r="L171" s="18" t="inlineStr">
         <is>
-          <t>Thermal payload sensors; Aerial photogrammetry analytics</t>
+          <t>ArcGIS spatial mapping, QGIS processing, Drone data capture systems</t>
         </is>
       </c>
       <c r="M171" s="15" t="inlineStr">
@@ -14755,14 +14759,10 @@
       <c r="O171" s="18" t="inlineStr"/>
       <c r="P171" s="18" t="inlineStr"/>
       <c r="Q171" s="18" t="inlineStr"/>
-      <c r="R171" s="18" t="inlineStr">
-        <is>
-          <t>+91 78744 00918</t>
-        </is>
-      </c>
+      <c r="R171" s="18" t="inlineStr"/>
       <c r="S171" s="17" t="inlineStr">
         <is>
-          <t>digitalbirddrones.com</t>
+          <t>https://hrpinfra.com</t>
         </is>
       </c>
       <c r="T171" s="18" t="inlineStr"/>
@@ -14778,16 +14778,16 @@
       </c>
       <c r="B172" s="12" t="inlineStr">
         <is>
-          <t>HRP Infra Pvt. Ltd.</t>
+          <t>Tassos Consultancy</t>
         </is>
       </c>
       <c r="C172" s="13" t="inlineStr">
         <is>
-          <t>https://hrpinfra.com</t>
+          <t>https://tassosconsultancy.com</t>
         </is>
       </c>
       <c r="D172" s="11" t="n">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="E172" s="14" t="inlineStr">
         <is>
@@ -14811,22 +14811,22 @@
       </c>
       <c r="I172" s="11" t="inlineStr">
         <is>
-          <t>20-100</t>
+          <t>10-50</t>
         </is>
       </c>
       <c r="J172" s="14" t="inlineStr">
         <is>
-          <t>Infrastructure consulting; GIS mapping services</t>
+          <t>GIS mapping; Drone analytics software integration</t>
         </is>
       </c>
       <c r="K172" s="14" t="inlineStr">
         <is>
-          <t>Urban infrastructure and utility asset mapping layout analysis</t>
+          <t>Energy, utility network, and precision vegetation asset management mapping</t>
         </is>
       </c>
       <c r="L172" s="14" t="inlineStr">
         <is>
-          <t>ArcGIS spatial mapping, QGIS processing, Drone data capture systems</t>
+          <t>Geospatial visual modeling, Digital drone mapping algorithms, GIS network layers</t>
         </is>
       </c>
       <c r="M172" s="11" t="inlineStr">
@@ -14838,39 +14838,47 @@
       <c r="O172" s="14" t="inlineStr"/>
       <c r="P172" s="14" t="inlineStr"/>
       <c r="Q172" s="14" t="inlineStr"/>
-      <c r="R172" s="14" t="inlineStr"/>
+      <c r="R172" s="14" t="inlineStr">
+        <is>
+          <t>+91 90336 08269</t>
+        </is>
+      </c>
       <c r="S172" s="13" t="inlineStr">
         <is>
-          <t>https://hrpinfra.com</t>
-        </is>
-      </c>
-      <c r="T172" s="14" t="inlineStr"/>
+          <t>https://tassosconsultancy.com</t>
+        </is>
+      </c>
+      <c r="T172" s="13" t="inlineStr">
+        <is>
+          <t>info@tassosconsultancy.com</t>
+        </is>
+      </c>
       <c r="U172" s="11" t="inlineStr">
         <is>
           <t>+91 / IN</t>
         </is>
       </c>
     </row>
-    <row r="173" ht="33" customHeight="1">
+    <row r="173" ht="46.5" customHeight="1">
       <c r="A173" s="15" t="n">
         <v>168</v>
       </c>
       <c r="B173" s="16" t="inlineStr">
         <is>
-          <t>Tassos Consultancy</t>
+          <t>GeoNomads Consulting LLP</t>
         </is>
       </c>
       <c r="C173" s="17" t="inlineStr">
         <is>
-          <t>https://tassosconsultancy.com</t>
+          <t>https://geonomads.in</t>
         </is>
       </c>
       <c r="D173" s="15" t="n">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="E173" s="18" t="inlineStr">
         <is>
-          <t>Ahmedabad, India</t>
+          <t>Gandhinagar, India</t>
         </is>
       </c>
       <c r="F173" s="18" t="inlineStr">
@@ -14885,27 +14893,27 @@
       </c>
       <c r="H173" s="18" t="inlineStr">
         <is>
-          <t>Private Company</t>
+          <t>Partnership</t>
         </is>
       </c>
       <c r="I173" s="15" t="inlineStr">
         <is>
-          <t>10-50</t>
+          <t>1-10</t>
         </is>
       </c>
       <c r="J173" s="18" t="inlineStr">
         <is>
-          <t>GIS mapping; Drone analytics software integration</t>
+          <t>Geospatial dashboards; WebGIS mapping systems</t>
         </is>
       </c>
       <c r="K173" s="18" t="inlineStr">
         <is>
-          <t>Energy, utility network, and precision vegetation asset management mapping</t>
+          <t>Advanced GeoAI analytics, terrain extraction under dense canopy, and infrastructure encroachment mapping</t>
         </is>
       </c>
       <c r="L173" s="18" t="inlineStr">
         <is>
-          <t>Geospatial visual modeling, Digital drone mapping algorithms, GIS network layers</t>
+          <t>LiDAR data classification software, geographic information systems, vector analysis engines</t>
         </is>
       </c>
       <c r="M173" s="15" t="inlineStr">
@@ -14919,19 +14927,15 @@
       <c r="Q173" s="18" t="inlineStr"/>
       <c r="R173" s="18" t="inlineStr">
         <is>
-          <t>+91 90336 08269</t>
+          <t>+91 98982 67565</t>
         </is>
       </c>
       <c r="S173" s="17" t="inlineStr">
         <is>
-          <t>https://tassosconsultancy.com</t>
-        </is>
-      </c>
-      <c r="T173" s="17" t="inlineStr">
-        <is>
-          <t>info@tassosconsultancy.com</t>
-        </is>
-      </c>
+          <t>https://geonomads.in</t>
+        </is>
+      </c>
+      <c r="T173" s="18" t="inlineStr"/>
       <c r="U173" s="15" t="inlineStr">
         <is>
           <t>+91 / IN</t>
@@ -14944,20 +14948,20 @@
       </c>
       <c r="B174" s="12" t="inlineStr">
         <is>
-          <t>GeoNomads Consulting LLP</t>
+          <t>TGIS</t>
         </is>
       </c>
       <c r="C174" s="13" t="inlineStr">
         <is>
-          <t>https://geonomads.in</t>
+          <t>http://www.tgis.co.in</t>
         </is>
       </c>
       <c r="D174" s="11" t="n">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="E174" s="14" t="inlineStr">
         <is>
-          <t>Gandhinagar, India</t>
+          <t>Ahmedabad, India</t>
         </is>
       </c>
       <c r="F174" s="14" t="inlineStr">
@@ -14972,27 +14976,27 @@
       </c>
       <c r="H174" s="14" t="inlineStr">
         <is>
-          <t>Partnership</t>
+          <t>Private Company</t>
         </is>
       </c>
       <c r="I174" s="11" t="inlineStr">
         <is>
-          <t>1-10</t>
+          <t>10-50</t>
         </is>
       </c>
       <c r="J174" s="14" t="inlineStr">
         <is>
-          <t>Geospatial dashboards; WebGIS mapping systems</t>
+          <t>Geospatial intelligence software; remote sensing datasets</t>
         </is>
       </c>
       <c r="K174" s="14" t="inlineStr">
         <is>
-          <t>Advanced GeoAI analytics, terrain extraction under dense canopy, and infrastructure encroachment mapping</t>
+          <t>High-resolution topographic modeling and structural corridor mapping using remote aerial sensors</t>
         </is>
       </c>
       <c r="L174" s="14" t="inlineStr">
         <is>
-          <t>LiDAR data classification software, geographic information systems, vector analysis engines</t>
+          <t>Custom digital elevation models, thematic GIS dashboards, drone data validation pipelines</t>
         </is>
       </c>
       <c r="M174" s="11" t="inlineStr">
@@ -15006,12 +15010,12 @@
       <c r="Q174" s="14" t="inlineStr"/>
       <c r="R174" s="14" t="inlineStr">
         <is>
-          <t>+91 98982 67565</t>
+          <t>+91 98981 20110</t>
         </is>
       </c>
       <c r="S174" s="13" t="inlineStr">
         <is>
-          <t>https://geonomads.in</t>
+          <t>http://www.tgis.co.in</t>
         </is>
       </c>
       <c r="T174" s="14" t="inlineStr"/>
@@ -15021,26 +15025,26 @@
         </is>
       </c>
     </row>
-    <row r="175" ht="46.5" customHeight="1">
+    <row r="175" ht="33" customHeight="1">
       <c r="A175" s="15" t="n">
         <v>170</v>
       </c>
       <c r="B175" s="16" t="inlineStr">
         <is>
-          <t>TGIS</t>
+          <t>DATAPKT Infra &amp; Geomatics</t>
         </is>
       </c>
       <c r="C175" s="17" t="inlineStr">
         <is>
-          <t>http://www.tgis.co.in</t>
+          <t>datapkt.com</t>
         </is>
       </c>
       <c r="D175" s="15" t="n">
-        <v>2015</v>
+        <v>2018</v>
       </c>
       <c r="E175" s="18" t="inlineStr">
         <is>
-          <t>Ahmedabad, India</t>
+          <t>Gurugram, India</t>
         </is>
       </c>
       <c r="F175" s="18" t="inlineStr">
@@ -15060,27 +15064,27 @@
       </c>
       <c r="I175" s="15" t="inlineStr">
         <is>
-          <t>10-50</t>
+          <t>11-50</t>
         </is>
       </c>
       <c r="J175" s="18" t="inlineStr">
         <is>
-          <t>Geospatial intelligence software; remote sensing datasets</t>
+          <t>Drone surveillance; asset mapping; thermal inspection services</t>
         </is>
       </c>
       <c r="K175" s="18" t="inlineStr">
         <is>
-          <t>High-resolution topographic modeling and structural corridor mapping using remote aerial sensors</t>
+          <t>Infrastructure inspection and thermal drone surveillance</t>
         </is>
       </c>
       <c r="L175" s="18" t="inlineStr">
         <is>
-          <t>Custom digital elevation models, thematic GIS dashboards, drone data validation pipelines</t>
+          <t>Thermal drone imaging; GIS mapping software</t>
         </is>
       </c>
       <c r="M175" s="15" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Offline</t>
         </is>
       </c>
       <c r="N175" s="18" t="inlineStr"/>
@@ -15089,12 +15093,12 @@
       <c r="Q175" s="18" t="inlineStr"/>
       <c r="R175" s="18" t="inlineStr">
         <is>
-          <t>+91 98981 20110</t>
+          <t>+91 84485 59100</t>
         </is>
       </c>
       <c r="S175" s="17" t="inlineStr">
         <is>
-          <t>http://www.tgis.co.in</t>
+          <t>datapkt.com</t>
         </is>
       </c>
       <c r="T175" s="18" t="inlineStr"/>
@@ -15110,20 +15114,20 @@
       </c>
       <c r="B176" s="12" t="inlineStr">
         <is>
-          <t>DATAPKT Infra &amp; Geomatics</t>
+          <t>Smaru Tech LLP</t>
         </is>
       </c>
       <c r="C176" s="13" t="inlineStr">
         <is>
-          <t>datapkt.com</t>
+          <t>smaru.in</t>
         </is>
       </c>
       <c r="D176" s="11" t="n">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="E176" s="14" t="inlineStr">
         <is>
-          <t>Gurugram, India</t>
+          <t>New Delhi, India</t>
         </is>
       </c>
       <c r="F176" s="14" t="inlineStr">
@@ -15148,17 +15152,17 @@
       </c>
       <c r="J176" s="14" t="inlineStr">
         <is>
-          <t>Drone surveillance; asset mapping; thermal inspection services</t>
+          <t>Automatic capacitor banks; drone powerline inspection services</t>
         </is>
       </c>
       <c r="K176" s="14" t="inlineStr">
         <is>
-          <t>Infrastructure inspection and thermal drone surveillance</t>
+          <t>Power quality solutions and drone powerline utilities monitoring</t>
         </is>
       </c>
       <c r="L176" s="14" t="inlineStr">
         <is>
-          <t>Thermal drone imaging; GIS mapping software</t>
+          <t>Drone-based inspection cameras; harmonic filters</t>
         </is>
       </c>
       <c r="M176" s="11" t="inlineStr">
@@ -15170,14 +15174,10 @@
       <c r="O176" s="14" t="inlineStr"/>
       <c r="P176" s="14" t="inlineStr"/>
       <c r="Q176" s="14" t="inlineStr"/>
-      <c r="R176" s="14" t="inlineStr">
-        <is>
-          <t>+91 84485 59100</t>
-        </is>
-      </c>
+      <c r="R176" s="14" t="inlineStr"/>
       <c r="S176" s="13" t="inlineStr">
         <is>
-          <t>datapkt.com</t>
+          <t>smaru.in</t>
         </is>
       </c>
       <c r="T176" s="14" t="inlineStr"/>
@@ -15193,20 +15193,20 @@
       </c>
       <c r="B177" s="16" t="inlineStr">
         <is>
-          <t>Smaru Tech LLP</t>
+          <t>Startflying Solution Private Limited</t>
         </is>
       </c>
       <c r="C177" s="17" t="inlineStr">
         <is>
-          <t>smaru.in</t>
+          <t>startflying.in</t>
         </is>
       </c>
       <c r="D177" s="15" t="n">
-        <v>2014</v>
+        <v>2021</v>
       </c>
       <c r="E177" s="18" t="inlineStr">
         <is>
-          <t>New Delhi, India</t>
+          <t>Gurugram, India</t>
         </is>
       </c>
       <c r="F177" s="18" t="inlineStr">
@@ -15226,22 +15226,22 @@
       </c>
       <c r="I177" s="15" t="inlineStr">
         <is>
-          <t>11-50</t>
+          <t>1-10</t>
         </is>
       </c>
       <c r="J177" s="18" t="inlineStr">
         <is>
-          <t>Automatic capacitor banks; drone powerline inspection services</t>
+          <t>Drone repair; drone mapping; night thermal surveillance services</t>
         </is>
       </c>
       <c r="K177" s="18" t="inlineStr">
         <is>
-          <t>Power quality solutions and drone powerline utilities monitoring</t>
+          <t>Night thermal surveillance and customized drone repair solutions</t>
         </is>
       </c>
       <c r="L177" s="18" t="inlineStr">
         <is>
-          <t>Drone-based inspection cameras; harmonic filters</t>
+          <t>Thermal surveillance drones</t>
         </is>
       </c>
       <c r="M177" s="15" t="inlineStr">
@@ -15253,10 +15253,14 @@
       <c r="O177" s="18" t="inlineStr"/>
       <c r="P177" s="18" t="inlineStr"/>
       <c r="Q177" s="18" t="inlineStr"/>
-      <c r="R177" s="18" t="inlineStr"/>
+      <c r="R177" s="18" t="inlineStr">
+        <is>
+          <t>+91 88099 91111</t>
+        </is>
+      </c>
       <c r="S177" s="17" t="inlineStr">
         <is>
-          <t>smaru.in</t>
+          <t>startflying.in</t>
         </is>
       </c>
       <c r="T177" s="18" t="inlineStr"/>
@@ -15272,16 +15276,16 @@
       </c>
       <c r="B178" s="12" t="inlineStr">
         <is>
-          <t>Startflying Solution Private Limited</t>
+          <t>Geoin Services</t>
         </is>
       </c>
       <c r="C178" s="13" t="inlineStr">
         <is>
-          <t>startflying.in</t>
+          <t>geoinservices.in</t>
         </is>
       </c>
       <c r="D178" s="11" t="n">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="E178" s="14" t="inlineStr">
         <is>
@@ -15305,22 +15309,22 @@
       </c>
       <c r="I178" s="11" t="inlineStr">
         <is>
-          <t>1-10</t>
+          <t>11-50</t>
         </is>
       </c>
       <c r="J178" s="14" t="inlineStr">
         <is>
-          <t>Drone repair; drone mapping; night thermal surveillance services</t>
+          <t>Subsurface utility engineering; drone mapping; GPR surveys</t>
         </is>
       </c>
       <c r="K178" s="14" t="inlineStr">
         <is>
-          <t>Night thermal surveillance and customized drone repair solutions</t>
+          <t>Subsurface utility engineering and ground penetrating radar mapping</t>
         </is>
       </c>
       <c r="L178" s="14" t="inlineStr">
         <is>
-          <t>Thermal surveillance drones</t>
+          <t>Ground penetrating radar; drone photogrammetry</t>
         </is>
       </c>
       <c r="M178" s="11" t="inlineStr">
@@ -15334,12 +15338,12 @@
       <c r="Q178" s="14" t="inlineStr"/>
       <c r="R178" s="14" t="inlineStr">
         <is>
-          <t>+91 88099 91111</t>
+          <t>+91 97175 23449</t>
         </is>
       </c>
       <c r="S178" s="13" t="inlineStr">
         <is>
-          <t>startflying.in</t>
+          <t>geoinservices.in</t>
         </is>
       </c>
       <c r="T178" s="14" t="inlineStr"/>
@@ -15355,16 +15359,16 @@
       </c>
       <c r="B179" s="16" t="inlineStr">
         <is>
-          <t>Geoin Services</t>
+          <t>Surveying India</t>
         </is>
       </c>
       <c r="C179" s="17" t="inlineStr">
         <is>
-          <t>geoinservices.in</t>
+          <t>surveyingindia.in</t>
         </is>
       </c>
       <c r="D179" s="15" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="E179" s="18" t="inlineStr">
         <is>
@@ -15393,17 +15397,17 @@
       </c>
       <c r="J179" s="18" t="inlineStr">
         <is>
-          <t>Subsurface utility engineering; drone mapping; GPR surveys</t>
+          <t>Aerial LiDAR; drone topographic surveying; corridor mapping</t>
         </is>
       </c>
       <c r="K179" s="18" t="inlineStr">
         <is>
-          <t>Subsurface utility engineering and ground penetrating radar mapping</t>
+          <t>Corridor mapping for utilities and drone-based terrain analysis</t>
         </is>
       </c>
       <c r="L179" s="18" t="inlineStr">
         <is>
-          <t>Ground penetrating radar; drone photogrammetry</t>
+          <t>Aerial LiDAR scanning; drone photogrammetry systems</t>
         </is>
       </c>
       <c r="M179" s="15" t="inlineStr">
@@ -15417,12 +15421,12 @@
       <c r="Q179" s="18" t="inlineStr"/>
       <c r="R179" s="18" t="inlineStr">
         <is>
-          <t>+91 97175 23449</t>
+          <t>+91 98718 80058</t>
         </is>
       </c>
       <c r="S179" s="17" t="inlineStr">
         <is>
-          <t>geoinservices.in</t>
+          <t>surveyingindia.in</t>
         </is>
       </c>
       <c r="T179" s="18" t="inlineStr"/>
@@ -15438,16 +15442,16 @@
       </c>
       <c r="B180" s="12" t="inlineStr">
         <is>
-          <t>Surveying India</t>
+          <t>DroneVerse Aviation Pvt. Ltd.</t>
         </is>
       </c>
       <c r="C180" s="13" t="inlineStr">
         <is>
-          <t>surveyingindia.in</t>
+          <t>droneverse.in</t>
         </is>
       </c>
       <c r="D180" s="11" t="n">
-        <v>2017</v>
+        <v>2022</v>
       </c>
       <c r="E180" s="14" t="inlineStr">
         <is>
@@ -15476,17 +15480,17 @@
       </c>
       <c r="J180" s="14" t="inlineStr">
         <is>
-          <t>Aerial LiDAR; drone topographic surveying; corridor mapping</t>
+          <t>Infrastructure drone inspections; aerial mapping solutions</t>
         </is>
       </c>
       <c r="K180" s="14" t="inlineStr">
         <is>
-          <t>Corridor mapping for utilities and drone-based terrain analysis</t>
+          <t>Cost-effective asset maintenance planning and visual tracking</t>
         </is>
       </c>
       <c r="L180" s="14" t="inlineStr">
         <is>
-          <t>Aerial LiDAR scanning; drone photogrammetry systems</t>
+          <t>Drone data analytics platforms</t>
         </is>
       </c>
       <c r="M180" s="11" t="inlineStr">
@@ -15498,14 +15502,10 @@
       <c r="O180" s="14" t="inlineStr"/>
       <c r="P180" s="14" t="inlineStr"/>
       <c r="Q180" s="14" t="inlineStr"/>
-      <c r="R180" s="14" t="inlineStr">
-        <is>
-          <t>+91 98718 80058</t>
-        </is>
-      </c>
+      <c r="R180" s="14" t="inlineStr"/>
       <c r="S180" s="13" t="inlineStr">
         <is>
-          <t>surveyingindia.in</t>
+          <t>droneverse.in</t>
         </is>
       </c>
       <c r="T180" s="14" t="inlineStr"/>
@@ -15515,22 +15515,22 @@
         </is>
       </c>
     </row>
-    <row r="181" ht="33" customHeight="1">
+    <row r="181" ht="46.5" customHeight="1">
       <c r="A181" s="15" t="n">
         <v>176</v>
       </c>
       <c r="B181" s="16" t="inlineStr">
         <is>
-          <t>DroneVerse Aviation Pvt. Ltd.</t>
+          <t>AeroDrone Robotics</t>
         </is>
       </c>
       <c r="C181" s="17" t="inlineStr">
         <is>
-          <t>droneverse.in</t>
+          <t>https://www.aerodronerobotics.com/</t>
         </is>
       </c>
       <c r="D181" s="15" t="n">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="E181" s="18" t="inlineStr">
         <is>
@@ -15549,7 +15549,7 @@
       </c>
       <c r="H181" s="18" t="inlineStr">
         <is>
-          <t>Private Company</t>
+          <t>Subsidiary of Innovision Limited</t>
         </is>
       </c>
       <c r="I181" s="15" t="inlineStr">
@@ -15559,35 +15559,43 @@
       </c>
       <c r="J181" s="18" t="inlineStr">
         <is>
-          <t>Infrastructure drone inspections; aerial mapping solutions</t>
+          <t>Industrial asset drone inspection; Aerial topographic mapping and surveying</t>
         </is>
       </c>
       <c r="K181" s="18" t="inlineStr">
         <is>
-          <t>Cost-effective asset maintenance planning and visual tracking</t>
+          <t>End-to-end drone inspection services and customized Drone-as-a-Service (DaaS) workflows for infrastructure and defense clients.</t>
         </is>
       </c>
       <c r="L181" s="18" t="inlineStr">
         <is>
-          <t>Drone data analytics platforms</t>
+          <t>LiDAR mapping systems, thermal imaging payloads, RTK-enabled survey drones.</t>
         </is>
       </c>
       <c r="M181" s="15" t="inlineStr">
         <is>
-          <t>Offline</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="N181" s="18" t="inlineStr"/>
       <c r="O181" s="18" t="inlineStr"/>
       <c r="P181" s="18" t="inlineStr"/>
       <c r="Q181" s="18" t="inlineStr"/>
-      <c r="R181" s="18" t="inlineStr"/>
+      <c r="R181" s="18" t="inlineStr">
+        <is>
+          <t>+91 96673 54466</t>
+        </is>
+      </c>
       <c r="S181" s="17" t="inlineStr">
         <is>
-          <t>droneverse.in</t>
-        </is>
-      </c>
-      <c r="T181" s="18" t="inlineStr"/>
+          <t>https://www.aerodronerobotics.com/</t>
+        </is>
+      </c>
+      <c r="T181" s="17" t="inlineStr">
+        <is>
+          <t>support@aerodronerobotics.com</t>
+        </is>
+      </c>
       <c r="U181" s="15" t="inlineStr">
         <is>
           <t>+91 / IN</t>
@@ -15600,16 +15608,16 @@
       </c>
       <c r="B182" s="12" t="inlineStr">
         <is>
-          <t>AeroDrone Robotics</t>
+          <t>AVPL International</t>
         </is>
       </c>
       <c r="C182" s="13" t="inlineStr">
         <is>
-          <t>https://www.aerodronerobotics.com/</t>
+          <t>https://avplinternational.com/</t>
         </is>
       </c>
       <c r="D182" s="11" t="n">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="E182" s="14" t="inlineStr">
         <is>
@@ -15628,27 +15636,27 @@
       </c>
       <c r="H182" s="14" t="inlineStr">
         <is>
-          <t>Subsidiary of Innovision Limited</t>
+          <t>Private Company</t>
         </is>
       </c>
       <c r="I182" s="11" t="inlineStr">
         <is>
-          <t>11-50</t>
+          <t>51-200</t>
         </is>
       </c>
       <c r="J182" s="14" t="inlineStr">
         <is>
-          <t>Industrial asset drone inspection; Aerial topographic mapping and surveying</t>
+          <t>Power-line drone inspection services; Drone GIS and corridor mapping</t>
         </is>
       </c>
       <c r="K182" s="14" t="inlineStr">
         <is>
-          <t>End-to-end drone inspection services and customized Drone-as-a-Service (DaaS) workflows for infrastructure and defense clients.</t>
+          <t>Drone-as-a-Service (DaaS) solutions for multi-utility infrastructure inspections and remote data processing.</t>
         </is>
       </c>
       <c r="L182" s="14" t="inlineStr">
         <is>
-          <t>LiDAR mapping systems, thermal imaging payloads, RTK-enabled survey drones.</t>
+          <t>Multi-rotor inspection drones, high-resolution RGB visual payloads, GIS mapping suites.</t>
         </is>
       </c>
       <c r="M182" s="11" t="inlineStr">
@@ -15662,17 +15670,17 @@
       <c r="Q182" s="14" t="inlineStr"/>
       <c r="R182" s="14" t="inlineStr">
         <is>
-          <t>+91 96673 54466</t>
+          <t>0124-420-2905</t>
         </is>
       </c>
       <c r="S182" s="13" t="inlineStr">
         <is>
-          <t>https://www.aerodronerobotics.com/</t>
+          <t>https://avplinternational.com/</t>
         </is>
       </c>
       <c r="T182" s="13" t="inlineStr">
         <is>
-          <t>support@aerodronerobotics.com</t>
+          <t>info@avplinternational.com</t>
         </is>
       </c>
       <c r="U182" s="11" t="inlineStr">
@@ -15687,16 +15695,16 @@
       </c>
       <c r="B183" s="16" t="inlineStr">
         <is>
-          <t>AVPL International</t>
+          <t>Global Dream Solution Private Limited</t>
         </is>
       </c>
       <c r="C183" s="17" t="inlineStr">
         <is>
-          <t>https://avplinternational.com/</t>
+          <t>https://gds-india.com/</t>
         </is>
       </c>
       <c r="D183" s="15" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="E183" s="18" t="inlineStr">
         <is>
@@ -15720,22 +15728,22 @@
       </c>
       <c r="I183" s="15" t="inlineStr">
         <is>
-          <t>51-200</t>
+          <t>11-50</t>
         </is>
       </c>
       <c r="J183" s="18" t="inlineStr">
         <is>
-          <t>Power-line drone inspection services; Drone GIS and corridor mapping</t>
+          <t>Industrial drone inspection services; Aerial utility infrastructure mapping</t>
         </is>
       </c>
       <c r="K183" s="18" t="inlineStr">
         <is>
-          <t>Drone-as-a-Service (DaaS) solutions for multi-utility infrastructure inspections and remote data processing.</t>
+          <t>Advanced unmanned aerial solutions optimized for critical infrastructure surveillance and multi-sensor industrial asset testing.</t>
         </is>
       </c>
       <c r="L183" s="18" t="inlineStr">
         <is>
-          <t>Multi-rotor inspection drones, high-resolution RGB visual payloads, GIS mapping suites.</t>
+          <t>Industrial inspection drones, radiometric thermal sensors, high-definition optical payloads.</t>
         </is>
       </c>
       <c r="M183" s="15" t="inlineStr">
@@ -15749,17 +15757,17 @@
       <c r="Q183" s="18" t="inlineStr"/>
       <c r="R183" s="18" t="inlineStr">
         <is>
-          <t>0124-420-2905</t>
+          <t>+91 97180 83346</t>
         </is>
       </c>
       <c r="S183" s="17" t="inlineStr">
         <is>
-          <t>https://avplinternational.com/</t>
+          <t>https://gds-india.com/</t>
         </is>
       </c>
       <c r="T183" s="17" t="inlineStr">
         <is>
-          <t>info@avplinternational.com</t>
+          <t>north@gds-india.com</t>
         </is>
       </c>
       <c r="U183" s="15" t="inlineStr">
@@ -15768,22 +15776,22 @@
         </is>
       </c>
     </row>
-    <row r="184" ht="46.5" customHeight="1">
+    <row r="184" ht="33" customHeight="1">
       <c r="A184" s="11" t="n">
         <v>179</v>
       </c>
       <c r="B184" s="12" t="inlineStr">
         <is>
-          <t>Global Dream Solution Private Limited</t>
+          <t>Vision Engineering Consultant</t>
         </is>
       </c>
       <c r="C184" s="13" t="inlineStr">
         <is>
-          <t>https://gds-india.com/</t>
+          <t>tradeindia.com</t>
         </is>
       </c>
       <c r="D184" s="11" t="n">
-        <v>2022</v>
+        <v>2012</v>
       </c>
       <c r="E184" s="14" t="inlineStr">
         <is>
@@ -15807,27 +15815,27 @@
       </c>
       <c r="I184" s="11" t="inlineStr">
         <is>
-          <t>11-50</t>
+          <t>5-20</t>
         </is>
       </c>
       <c r="J184" s="14" t="inlineStr">
         <is>
-          <t>Industrial drone inspection services; Aerial utility infrastructure mapping</t>
+          <t>UAV mapping surveys; Topographic land documentation</t>
         </is>
       </c>
       <c r="K184" s="14" t="inlineStr">
         <is>
-          <t>Advanced unmanned aerial solutions optimized for critical infrastructure surveillance and multi-sensor industrial asset testing.</t>
+          <t>Terrain elevations, utility lines monitoring, and high-accuracy contour profiling.</t>
         </is>
       </c>
       <c r="L184" s="14" t="inlineStr">
         <is>
-          <t>Industrial inspection drones, radiometric thermal sensors, high-definition optical payloads.</t>
+          <t>Aerial photogrammetry mapping workflows and total station surveying data correlation.</t>
         </is>
       </c>
       <c r="M184" s="11" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Offline</t>
         </is>
       </c>
       <c r="N184" s="14" t="inlineStr"/>
@@ -15836,41 +15844,37 @@
       <c r="Q184" s="14" t="inlineStr"/>
       <c r="R184" s="14" t="inlineStr">
         <is>
-          <t>+91 97180 83346</t>
+          <t>+91 72900 18471</t>
         </is>
       </c>
       <c r="S184" s="13" t="inlineStr">
         <is>
-          <t>https://gds-india.com/</t>
-        </is>
-      </c>
-      <c r="T184" s="13" t="inlineStr">
-        <is>
-          <t>north@gds-india.com</t>
-        </is>
-      </c>
+          <t>tradeindia.com</t>
+        </is>
+      </c>
+      <c r="T184" s="14" t="inlineStr"/>
       <c r="U184" s="11" t="inlineStr">
         <is>
           <t>+91 / IN</t>
         </is>
       </c>
     </row>
-    <row r="185" ht="33" customHeight="1">
+    <row r="185" ht="46.5" customHeight="1">
       <c r="A185" s="15" t="n">
         <v>180</v>
       </c>
       <c r="B185" s="16" t="inlineStr">
         <is>
-          <t>Vision Engineering Consultant</t>
+          <t>Unique Solutions</t>
         </is>
       </c>
       <c r="C185" s="17" t="inlineStr">
         <is>
-          <t>tradeindia.com</t>
+          <t>uniquesolutionsweb.com</t>
         </is>
       </c>
       <c r="D185" s="15" t="n">
-        <v>2012</v>
+        <v>2015</v>
       </c>
       <c r="E185" s="18" t="inlineStr">
         <is>
@@ -15894,41 +15898,49 @@
       </c>
       <c r="I185" s="15" t="inlineStr">
         <is>
-          <t>5-20</t>
+          <t>11-50</t>
         </is>
       </c>
       <c r="J185" s="18" t="inlineStr">
         <is>
-          <t>UAV mapping surveys; Topographic land documentation</t>
+          <t>Aerial drone surveying; GIS mapping services</t>
         </is>
       </c>
       <c r="K185" s="18" t="inlineStr">
         <is>
-          <t>Terrain elevations, utility lines monitoring, and high-accuracy contour profiling.</t>
+          <t>Topographic land mapping, revenue analysis, and aerial corridor inspection using customized UAV workflows.</t>
         </is>
       </c>
       <c r="L185" s="18" t="inlineStr">
         <is>
-          <t>Aerial photogrammetry mapping workflows and total station surveying data correlation.</t>
+          <t>Photogrammetry software, DGPS topography equipment, and multi-rotor camera drones.</t>
         </is>
       </c>
       <c r="M185" s="15" t="inlineStr">
         <is>
-          <t>Offline</t>
-        </is>
-      </c>
-      <c r="N185" s="18" t="inlineStr"/>
-      <c r="O185" s="18" t="inlineStr"/>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="N185" s="18" t="inlineStr">
+        <is>
+          <t>Parveen Dahiya</t>
+        </is>
+      </c>
+      <c r="O185" s="18" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
       <c r="P185" s="18" t="inlineStr"/>
       <c r="Q185" s="18" t="inlineStr"/>
       <c r="R185" s="18" t="inlineStr">
         <is>
-          <t>+91 72900 18471</t>
+          <t>+91 95403 21111</t>
         </is>
       </c>
       <c r="S185" s="17" t="inlineStr">
         <is>
-          <t>tradeindia.com</t>
+          <t>uniquesolutionsweb.com</t>
         </is>
       </c>
       <c r="T185" s="18" t="inlineStr"/>
@@ -15938,22 +15950,22 @@
         </is>
       </c>
     </row>
-    <row r="186" ht="46.5" customHeight="1">
+    <row r="186" ht="33" customHeight="1">
       <c r="A186" s="11" t="n">
         <v>181</v>
       </c>
       <c r="B186" s="12" t="inlineStr">
         <is>
-          <t>Unique Solutions</t>
+          <t>Innovision Limited</t>
         </is>
       </c>
       <c r="C186" s="13" t="inlineStr">
         <is>
-          <t>uniquesolutionsweb.com</t>
+          <t>innovision.co.in</t>
         </is>
       </c>
       <c r="D186" s="11" t="n">
-        <v>2015</v>
+        <v>2007</v>
       </c>
       <c r="E186" s="14" t="inlineStr">
         <is>
@@ -15972,27 +15984,27 @@
       </c>
       <c r="H186" s="14" t="inlineStr">
         <is>
-          <t>Private Company</t>
+          <t>Public Company</t>
         </is>
       </c>
       <c r="I186" s="11" t="inlineStr">
         <is>
-          <t>11-50</t>
+          <t>10,000-15,000</t>
         </is>
       </c>
       <c r="J186" s="14" t="inlineStr">
         <is>
-          <t>Aerial drone surveying; GIS mapping services</t>
+          <t>Manpower services; integrated infrastructure security; electronic surveillance</t>
         </is>
       </c>
       <c r="K186" s="14" t="inlineStr">
         <is>
-          <t>Topographic land mapping, revenue analysis, and aerial corridor inspection using customized UAV workflows.</t>
+          <t>Drone-enabled facility and infrastructure asset inspection</t>
         </is>
       </c>
       <c r="L186" s="14" t="inlineStr">
         <is>
-          <t>Photogrammetry software, DGPS topography equipment, and multi-rotor camera drones.</t>
+          <t>Surveillance drones, thermal inspection payloads</t>
         </is>
       </c>
       <c r="M186" s="11" t="inlineStr">
@@ -16002,24 +16014,24 @@
       </c>
       <c r="N186" s="14" t="inlineStr">
         <is>
-          <t>Parveen Dahiya</t>
+          <t>Randeep Hundal</t>
         </is>
       </c>
       <c r="O186" s="14" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Chairman and Managing Director</t>
         </is>
       </c>
       <c r="P186" s="14" t="inlineStr"/>
       <c r="Q186" s="14" t="inlineStr"/>
       <c r="R186" s="14" t="inlineStr">
         <is>
-          <t>+91 95403 21111</t>
+          <t>+91 124 234 1602</t>
         </is>
       </c>
       <c r="S186" s="13" t="inlineStr">
         <is>
-          <t>uniquesolutionsweb.com</t>
+          <t>innovision.co.in</t>
         </is>
       </c>
       <c r="T186" s="14" t="inlineStr"/>
@@ -16035,16 +16047,16 @@
       </c>
       <c r="B187" s="16" t="inlineStr">
         <is>
-          <t>Innovision Limited</t>
+          <t>NVA Infracon</t>
         </is>
       </c>
       <c r="C187" s="17" t="inlineStr">
         <is>
-          <t>innovision.co.in</t>
+          <t>nvainfracon.com</t>
         </is>
       </c>
       <c r="D187" s="15" t="n">
-        <v>2007</v>
+        <v>2020</v>
       </c>
       <c r="E187" s="18" t="inlineStr">
         <is>
@@ -16063,54 +16075,42 @@
       </c>
       <c r="H187" s="18" t="inlineStr">
         <is>
-          <t>Public Company</t>
+          <t>Private Company</t>
         </is>
       </c>
       <c r="I187" s="15" t="inlineStr">
         <is>
-          <t>10,000-15,000</t>
+          <t>10-50</t>
         </is>
       </c>
       <c r="J187" s="18" t="inlineStr">
         <is>
-          <t>Manpower services; integrated infrastructure security; electronic surveillance</t>
+          <t>GIS cadastral mapping; corridor scan analytics</t>
         </is>
       </c>
       <c r="K187" s="18" t="inlineStr">
         <is>
-          <t>Drone-enabled facility and infrastructure asset inspection</t>
+          <t>Canopy layer mapping and high-precision corridor alignment tracing</t>
         </is>
       </c>
       <c r="L187" s="18" t="inlineStr">
         <is>
-          <t>Surveillance drones, thermal inspection payloads</t>
+          <t>DGPS receivers, vegetation canopy penetration LiDAR systems</t>
         </is>
       </c>
       <c r="M187" s="15" t="inlineStr">
         <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="N187" s="18" t="inlineStr">
-        <is>
-          <t>Randeep Hundal</t>
-        </is>
-      </c>
-      <c r="O187" s="18" t="inlineStr">
-        <is>
-          <t>Chairman and Managing Director</t>
-        </is>
-      </c>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="N187" s="18" t="inlineStr"/>
+      <c r="O187" s="18" t="inlineStr"/>
       <c r="P187" s="18" t="inlineStr"/>
       <c r="Q187" s="18" t="inlineStr"/>
-      <c r="R187" s="18" t="inlineStr">
-        <is>
-          <t>+91 124 234 1602</t>
-        </is>
-      </c>
+      <c r="R187" s="18" t="inlineStr"/>
       <c r="S187" s="17" t="inlineStr">
         <is>
-          <t>innovision.co.in</t>
+          <t>nvainfracon.com</t>
         </is>
       </c>
       <c r="T187" s="18" t="inlineStr"/>
@@ -16126,20 +16126,20 @@
       </c>
       <c r="B188" s="12" t="inlineStr">
         <is>
-          <t>NVA Infracon</t>
+          <t>Skyglimps Technologies LLP</t>
         </is>
       </c>
       <c r="C188" s="13" t="inlineStr">
         <is>
-          <t>nvainfracon.com</t>
+          <t>skyglimps.com</t>
         </is>
       </c>
       <c r="D188" s="11" t="n">
-        <v>2020</v>
+        <v>2024</v>
       </c>
       <c r="E188" s="14" t="inlineStr">
         <is>
-          <t>Gurugram, India</t>
+          <t>Kolkata, India</t>
         </is>
       </c>
       <c r="F188" s="14" t="inlineStr">
@@ -16159,27 +16159,27 @@
       </c>
       <c r="I188" s="11" t="inlineStr">
         <is>
-          <t>10-50</t>
+          <t>11-50</t>
         </is>
       </c>
       <c r="J188" s="14" t="inlineStr">
         <is>
-          <t>GIS cadastral mapping; corridor scan analytics</t>
+          <t>Aerial surveying data services; infrastructure inspection analytics</t>
         </is>
       </c>
       <c r="K188" s="14" t="inlineStr">
         <is>
-          <t>Canopy layer mapping and high-precision corridor alignment tracing</t>
+          <t>High-precision aerial intelligence and drone pilot training for critical sectors</t>
         </is>
       </c>
       <c r="L188" s="14" t="inlineStr">
         <is>
-          <t>DGPS receivers, vegetation canopy penetration LiDAR systems</t>
+          <t>LiDAR sensors, thermal cameras, and RGB aerial payloads</t>
         </is>
       </c>
       <c r="M188" s="11" t="inlineStr">
         <is>
-          <t>Offline</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="N188" s="14" t="inlineStr"/>
@@ -16189,7 +16189,7 @@
       <c r="R188" s="14" t="inlineStr"/>
       <c r="S188" s="13" t="inlineStr">
         <is>
-          <t>nvainfracon.com</t>
+          <t>skyglimps.com</t>
         </is>
       </c>
       <c r="T188" s="14" t="inlineStr"/>
@@ -16205,16 +16205,16 @@
       </c>
       <c r="B189" s="16" t="inlineStr">
         <is>
-          <t>Skyglimps Technologies LLP</t>
+          <t>Rchobbytech Solutions Private Limited</t>
         </is>
       </c>
       <c r="C189" s="17" t="inlineStr">
         <is>
-          <t>skyglimps.com</t>
+          <t>rchobbytech.in</t>
         </is>
       </c>
       <c r="D189" s="15" t="n">
-        <v>2024</v>
+        <v>2004</v>
       </c>
       <c r="E189" s="18" t="inlineStr">
         <is>
@@ -16238,22 +16238,22 @@
       </c>
       <c r="I189" s="15" t="inlineStr">
         <is>
-          <t>11-50</t>
+          <t>10-50</t>
         </is>
       </c>
       <c r="J189" s="18" t="inlineStr">
         <is>
-          <t>Aerial surveying data services; infrastructure inspection analytics</t>
+          <t>Power line inspection solutions; environmental surveillance drones</t>
         </is>
       </c>
       <c r="K189" s="18" t="inlineStr">
         <is>
-          <t>High-precision aerial intelligence and drone pilot training for critical sectors</t>
+          <t>UAV-based thermal fault inspection and RTK PPK mapping solutions</t>
         </is>
       </c>
       <c r="L189" s="18" t="inlineStr">
         <is>
-          <t>LiDAR sensors, thermal cameras, and RGB aerial payloads</t>
+          <t>RTK PPK mapping drones and LiDAR scanning payloads</t>
         </is>
       </c>
       <c r="M189" s="15" t="inlineStr">
@@ -16268,7 +16268,7 @@
       <c r="R189" s="18" t="inlineStr"/>
       <c r="S189" s="17" t="inlineStr">
         <is>
-          <t>skyglimps.com</t>
+          <t>rchobbytech.in</t>
         </is>
       </c>
       <c r="T189" s="18" t="inlineStr"/>
@@ -16284,16 +16284,16 @@
       </c>
       <c r="B190" s="12" t="inlineStr">
         <is>
-          <t>Rchobbytech Solutions Private Limited</t>
+          <t>M I B Engineering &amp; Consultants Pvt. Ltd.</t>
         </is>
       </c>
       <c r="C190" s="13" t="inlineStr">
         <is>
-          <t>rchobbytech.in</t>
+          <t>mibengineering.in</t>
         </is>
       </c>
       <c r="D190" s="11" t="n">
-        <v>2004</v>
+        <v>2012</v>
       </c>
       <c r="E190" s="14" t="inlineStr">
         <is>
@@ -16307,7 +16307,7 @@
       </c>
       <c r="G190" s="14" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>India; Bhutan; Bangladesh</t>
         </is>
       </c>
       <c r="H190" s="14" t="inlineStr">
@@ -16317,22 +16317,22 @@
       </c>
       <c r="I190" s="11" t="inlineStr">
         <is>
-          <t>10-50</t>
+          <t>100-250</t>
         </is>
       </c>
       <c r="J190" s="14" t="inlineStr">
         <is>
-          <t>Power line inspection solutions; environmental surveillance drones</t>
+          <t>Turnkey electrical engineering; industrial drone inspection services</t>
         </is>
       </c>
       <c r="K190" s="14" t="inlineStr">
         <is>
-          <t>UAV-based thermal fault inspection and RTK PPK mapping solutions</t>
+          <t>Substation maintenance, detail engineering design, and aerial asset integrity checks</t>
         </is>
       </c>
       <c r="L190" s="14" t="inlineStr">
         <is>
-          <t>RTK PPK mapping drones and LiDAR scanning payloads</t>
+          <t>Drone visual imaging and thermal analysis systems</t>
         </is>
       </c>
       <c r="M190" s="11" t="inlineStr">
@@ -16347,7 +16347,7 @@
       <c r="R190" s="14" t="inlineStr"/>
       <c r="S190" s="13" t="inlineStr">
         <is>
-          <t>rchobbytech.in</t>
+          <t>mibengineering.in</t>
         </is>
       </c>
       <c r="T190" s="14" t="inlineStr"/>
@@ -16357,22 +16357,22 @@
         </is>
       </c>
     </row>
-    <row r="191" ht="33" customHeight="1">
+    <row r="191" ht="46.5" customHeight="1">
       <c r="A191" s="15" t="n">
         <v>186</v>
       </c>
       <c r="B191" s="16" t="inlineStr">
         <is>
-          <t>M I B Engineering &amp; Consultants Pvt. Ltd.</t>
+          <t>Constell Consultants Pvt. Ltd.</t>
         </is>
       </c>
       <c r="C191" s="17" t="inlineStr">
         <is>
-          <t>mibengineering.in</t>
+          <t>constellconsultants.in</t>
         </is>
       </c>
       <c r="D191" s="15" t="n">
-        <v>2012</v>
+        <v>1984</v>
       </c>
       <c r="E191" s="18" t="inlineStr">
         <is>
@@ -16386,7 +16386,7 @@
       </c>
       <c r="G191" s="18" t="inlineStr">
         <is>
-          <t>India; Bhutan; Bangladesh</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H191" s="18" t="inlineStr">
@@ -16396,22 +16396,22 @@
       </c>
       <c r="I191" s="15" t="inlineStr">
         <is>
-          <t>100-250</t>
+          <t>10-50</t>
         </is>
       </c>
       <c r="J191" s="18" t="inlineStr">
         <is>
-          <t>Turnkey electrical engineering; industrial drone inspection services</t>
+          <t>Geotechnical engineering investigations; transmission corridor mapping</t>
         </is>
       </c>
       <c r="K191" s="18" t="inlineStr">
         <is>
-          <t>Substation maintenance, detail engineering design, and aerial asset integrity checks</t>
+          <t>Topographic surveys and stability investigations for transmission towers and power plants</t>
         </is>
       </c>
       <c r="L191" s="18" t="inlineStr">
         <is>
-          <t>Drone visual imaging and thermal analysis systems</t>
+          <t>Total station instrumentation and drone topographic surveying methodologies</t>
         </is>
       </c>
       <c r="M191" s="15" t="inlineStr">
@@ -16426,7 +16426,7 @@
       <c r="R191" s="18" t="inlineStr"/>
       <c r="S191" s="17" t="inlineStr">
         <is>
-          <t>mibengineering.in</t>
+          <t>constellconsultants.in</t>
         </is>
       </c>
       <c r="T191" s="18" t="inlineStr"/>
@@ -16436,22 +16436,22 @@
         </is>
       </c>
     </row>
-    <row r="192" ht="46.5" customHeight="1">
+    <row r="192" ht="33" customHeight="1">
       <c r="A192" s="11" t="n">
         <v>187</v>
       </c>
       <c r="B192" s="12" t="inlineStr">
         <is>
-          <t>Constell Consultants Pvt. Ltd.</t>
+          <t>Absolute Surveying</t>
         </is>
       </c>
       <c r="C192" s="13" t="inlineStr">
         <is>
-          <t>constellconsultants.in</t>
+          <t>absolutesurveying.co.in</t>
         </is>
       </c>
       <c r="D192" s="11" t="n">
-        <v>1984</v>
+        <v>2017</v>
       </c>
       <c r="E192" s="14" t="inlineStr">
         <is>
@@ -16475,22 +16475,22 @@
       </c>
       <c r="I192" s="11" t="inlineStr">
         <is>
-          <t>10-50</t>
+          <t>10-30</t>
         </is>
       </c>
       <c r="J192" s="14" t="inlineStr">
         <is>
-          <t>Geotechnical engineering investigations; transmission corridor mapping</t>
+          <t>Land topographic surveying; drone mapping solutions</t>
         </is>
       </c>
       <c r="K192" s="14" t="inlineStr">
         <is>
-          <t>Topographic surveys and stability investigations for transmission towers and power plants</t>
+          <t>Transmission line corridor engineering profiling and GNSS data integration</t>
         </is>
       </c>
       <c r="L192" s="14" t="inlineStr">
         <is>
-          <t>Total station instrumentation and drone topographic surveying methodologies</t>
+          <t>Surveyaan V1 survey drones and GNSS receiver systems</t>
         </is>
       </c>
       <c r="M192" s="11" t="inlineStr">
@@ -16505,7 +16505,7 @@
       <c r="R192" s="14" t="inlineStr"/>
       <c r="S192" s="13" t="inlineStr">
         <is>
-          <t>constellconsultants.in</t>
+          <t>absolutesurveying.co.in</t>
         </is>
       </c>
       <c r="T192" s="14" t="inlineStr"/>
@@ -16521,16 +16521,16 @@
       </c>
       <c r="B193" s="16" t="inlineStr">
         <is>
-          <t>Absolute Surveying</t>
+          <t>Aeroscan Technology LLP</t>
         </is>
       </c>
       <c r="C193" s="17" t="inlineStr">
         <is>
-          <t>absolutesurveying.co.in</t>
+          <t>aeroscantechnology.com</t>
         </is>
       </c>
       <c r="D193" s="15" t="n">
-        <v>2017</v>
+        <v>2024</v>
       </c>
       <c r="E193" s="18" t="inlineStr">
         <is>
@@ -16554,22 +16554,22 @@
       </c>
       <c r="I193" s="15" t="inlineStr">
         <is>
-          <t>10-30</t>
+          <t>1-10</t>
         </is>
       </c>
       <c r="J193" s="18" t="inlineStr">
         <is>
-          <t>Land topographic surveying; drone mapping solutions</t>
+          <t>UAV aerial data capture; LiDAR data processing</t>
         </is>
       </c>
       <c r="K193" s="18" t="inlineStr">
         <is>
-          <t>Transmission line corridor engineering profiling and GNSS data integration</t>
+          <t>AI-enhanced drone geospatial analytics for infrastructure and utilities</t>
         </is>
       </c>
       <c r="L193" s="18" t="inlineStr">
         <is>
-          <t>Surveyaan V1 survey drones and GNSS receiver systems</t>
+          <t>LiDAR sensors; thermal imaging payloads; RGB cameras</t>
         </is>
       </c>
       <c r="M193" s="15" t="inlineStr">
@@ -16577,17 +16577,33 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="N193" s="18" t="inlineStr"/>
-      <c r="O193" s="18" t="inlineStr"/>
+      <c r="N193" s="18" t="inlineStr">
+        <is>
+          <t>Ashis Poddar</t>
+        </is>
+      </c>
+      <c r="O193" s="18" t="inlineStr">
+        <is>
+          <t>Founder &amp; CEO</t>
+        </is>
+      </c>
       <c r="P193" s="18" t="inlineStr"/>
       <c r="Q193" s="18" t="inlineStr"/>
-      <c r="R193" s="18" t="inlineStr"/>
+      <c r="R193" s="18" t="inlineStr">
+        <is>
+          <t>+91 9903002494</t>
+        </is>
+      </c>
       <c r="S193" s="17" t="inlineStr">
         <is>
-          <t>absolutesurveying.co.in</t>
-        </is>
-      </c>
-      <c r="T193" s="18" t="inlineStr"/>
+          <t>aeroscantechnology.com</t>
+        </is>
+      </c>
+      <c r="T193" s="17" t="inlineStr">
+        <is>
+          <t>info@aeroscantechnology.com</t>
+        </is>
+      </c>
       <c r="U193" s="15" t="inlineStr">
         <is>
           <t>+91 / IN</t>
@@ -16600,16 +16616,16 @@
       </c>
       <c r="B194" s="12" t="inlineStr">
         <is>
-          <t>Aeroscan Technology LLP</t>
+          <t>Kesowa Infinite Ventures Private Limited</t>
         </is>
       </c>
       <c r="C194" s="13" t="inlineStr">
         <is>
-          <t>aeroscantechnology.com</t>
+          <t>https://www.kesowa.in</t>
         </is>
       </c>
       <c r="D194" s="11" t="n">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="E194" s="14" t="inlineStr">
         <is>
@@ -16633,22 +16649,22 @@
       </c>
       <c r="I194" s="11" t="inlineStr">
         <is>
-          <t>1-10</t>
+          <t>20-50</t>
         </is>
       </c>
       <c r="J194" s="14" t="inlineStr">
         <is>
-          <t>UAV aerial data capture; LiDAR data processing</t>
+          <t>Drone inspection services; cloud-based GIS platforms</t>
         </is>
       </c>
       <c r="K194" s="14" t="inlineStr">
         <is>
-          <t>AI-enhanced drone geospatial analytics for infrastructure and utilities</t>
+          <t>Centralized drone data call centers and transmission grid mapping</t>
         </is>
       </c>
       <c r="L194" s="14" t="inlineStr">
         <is>
-          <t>LiDAR sensors; thermal imaging payloads; RGB cameras</t>
+          <t>ARU Server drone data platform; high-resolution optical and thermal payloads</t>
         </is>
       </c>
       <c r="M194" s="11" t="inlineStr">
@@ -16658,7 +16674,7 @@
       </c>
       <c r="N194" s="14" t="inlineStr">
         <is>
-          <t>Ashis Poddar</t>
+          <t>Prayush Poddar</t>
         </is>
       </c>
       <c r="O194" s="14" t="inlineStr">
@@ -16670,19 +16686,15 @@
       <c r="Q194" s="14" t="inlineStr"/>
       <c r="R194" s="14" t="inlineStr">
         <is>
-          <t>+91 9903002494</t>
+          <t>+91 7003961082</t>
         </is>
       </c>
       <c r="S194" s="13" t="inlineStr">
         <is>
-          <t>aeroscantechnology.com</t>
-        </is>
-      </c>
-      <c r="T194" s="13" t="inlineStr">
-        <is>
-          <t>info@aeroscantechnology.com</t>
-        </is>
-      </c>
+          <t>https://www.kesowa.in</t>
+        </is>
+      </c>
+      <c r="T194" s="14" t="inlineStr"/>
       <c r="U194" s="11" t="inlineStr">
         <is>
           <t>+91 / IN</t>
@@ -16695,16 +16707,16 @@
       </c>
       <c r="B195" s="16" t="inlineStr">
         <is>
-          <t>Kesowa Infinite Ventures Private Limited</t>
+          <t>Spatem GeoTeck Private Limited</t>
         </is>
       </c>
       <c r="C195" s="17" t="inlineStr">
         <is>
-          <t>https://www.kesowa.in</t>
+          <t>https://geoteck.co.in</t>
         </is>
       </c>
       <c r="D195" s="15" t="n">
-        <v>2020</v>
+        <v>2023</v>
       </c>
       <c r="E195" s="18" t="inlineStr">
         <is>
@@ -16728,22 +16740,22 @@
       </c>
       <c r="I195" s="15" t="inlineStr">
         <is>
-          <t>20-50</t>
+          <t>1-10</t>
         </is>
       </c>
       <c r="J195" s="18" t="inlineStr">
         <is>
-          <t>Drone inspection services; cloud-based GIS platforms</t>
+          <t>UAV drone surveys; LiDAR and SAR data processing</t>
         </is>
       </c>
       <c r="K195" s="18" t="inlineStr">
         <is>
-          <t>Centralized drone data call centers and transmission grid mapping</t>
+          <t>Geospatial mapping and high-precision infrastructure aerial survey</t>
         </is>
       </c>
       <c r="L195" s="18" t="inlineStr">
         <is>
-          <t>ARU Server drone data platform; high-resolution optical and thermal payloads</t>
+          <t>LiDAR mapping drone payloads; WebGIS dashboard systems</t>
         </is>
       </c>
       <c r="M195" s="15" t="inlineStr">
@@ -16751,47 +16763,39 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="N195" s="18" t="inlineStr">
-        <is>
-          <t>Prayush Poddar</t>
-        </is>
-      </c>
-      <c r="O195" s="18" t="inlineStr">
-        <is>
-          <t>Founder &amp; CEO</t>
-        </is>
-      </c>
+      <c r="N195" s="18" t="inlineStr"/>
+      <c r="O195" s="18" t="inlineStr"/>
       <c r="P195" s="18" t="inlineStr"/>
       <c r="Q195" s="18" t="inlineStr"/>
-      <c r="R195" s="18" t="inlineStr">
-        <is>
-          <t>+91 7003961082</t>
-        </is>
-      </c>
+      <c r="R195" s="18" t="inlineStr"/>
       <c r="S195" s="17" t="inlineStr">
         <is>
-          <t>https://www.kesowa.in</t>
-        </is>
-      </c>
-      <c r="T195" s="18" t="inlineStr"/>
+          <t>https://geoteck.co.in</t>
+        </is>
+      </c>
+      <c r="T195" s="17" t="inlineStr">
+        <is>
+          <t>support@geoteck.org</t>
+        </is>
+      </c>
       <c r="U195" s="15" t="inlineStr">
         <is>
           <t>+91 / IN</t>
         </is>
       </c>
     </row>
-    <row r="196" ht="33" customHeight="1">
+    <row r="196" ht="46.5" customHeight="1">
       <c r="A196" s="11" t="n">
         <v>191</v>
       </c>
       <c r="B196" s="12" t="inlineStr">
         <is>
-          <t>Spatem GeoTeck Private Limited</t>
+          <t>FalconRise AvianTech</t>
         </is>
       </c>
       <c r="C196" s="13" t="inlineStr">
         <is>
-          <t>https://geoteck.co.in</t>
+          <t>falconrise.in</t>
         </is>
       </c>
       <c r="D196" s="11" t="n">
@@ -16824,17 +16828,17 @@
       </c>
       <c r="J196" s="14" t="inlineStr">
         <is>
-          <t>UAV drone surveys; LiDAR and SAR data processing</t>
+          <t>Aerial asset inspection; Surveying imagery</t>
         </is>
       </c>
       <c r="K196" s="14" t="inlineStr">
         <is>
-          <t>Geospatial mapping and high-precision infrastructure aerial survey</t>
+          <t>Industrial data collection and corridor visibility analytics</t>
         </is>
       </c>
       <c r="L196" s="14" t="inlineStr">
         <is>
-          <t>LiDAR mapping drone payloads; WebGIS dashboard systems</t>
+          <t>High-resolution digital mapping, AI-driven data processing, multi-rotor inspection setups</t>
         </is>
       </c>
       <c r="M196" s="11" t="inlineStr">
@@ -16846,39 +16850,39 @@
       <c r="O196" s="14" t="inlineStr"/>
       <c r="P196" s="14" t="inlineStr"/>
       <c r="Q196" s="14" t="inlineStr"/>
-      <c r="R196" s="14" t="inlineStr"/>
+      <c r="R196" s="14" t="inlineStr">
+        <is>
+          <t>+91 89026 72625</t>
+        </is>
+      </c>
       <c r="S196" s="13" t="inlineStr">
         <is>
-          <t>https://geoteck.co.in</t>
-        </is>
-      </c>
-      <c r="T196" s="13" t="inlineStr">
-        <is>
-          <t>support@geoteck.org</t>
-        </is>
-      </c>
+          <t>falconrise.in</t>
+        </is>
+      </c>
+      <c r="T196" s="14" t="inlineStr"/>
       <c r="U196" s="11" t="inlineStr">
         <is>
           <t>+91 / IN</t>
         </is>
       </c>
     </row>
-    <row r="197" ht="46.5" customHeight="1">
+    <row r="197" ht="33" customHeight="1">
       <c r="A197" s="15" t="n">
         <v>192</v>
       </c>
       <c r="B197" s="16" t="inlineStr">
         <is>
-          <t>FalconRise AvianTech</t>
+          <t>CyberSWIFT Infotech Private Limited</t>
         </is>
       </c>
       <c r="C197" s="17" t="inlineStr">
         <is>
-          <t>falconrise.in</t>
+          <t>cyberswift.com</t>
         </is>
       </c>
       <c r="D197" s="15" t="n">
-        <v>2023</v>
+        <v>2008</v>
       </c>
       <c r="E197" s="18" t="inlineStr">
         <is>
@@ -16887,12 +16891,12 @@
       </c>
       <c r="F197" s="18" t="inlineStr">
         <is>
-          <t>APAC(India)</t>
+          <t>NA(United States); APAC(India)</t>
         </is>
       </c>
       <c r="G197" s="18" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>India; United States</t>
         </is>
       </c>
       <c r="H197" s="18" t="inlineStr">
@@ -16902,22 +16906,22 @@
       </c>
       <c r="I197" s="15" t="inlineStr">
         <is>
-          <t>1-10</t>
+          <t>100-500</t>
         </is>
       </c>
       <c r="J197" s="18" t="inlineStr">
         <is>
-          <t>Aerial asset inspection; Surveying imagery</t>
+          <t>GIS spatial analytics; utility network data mapping</t>
         </is>
       </c>
       <c r="K197" s="18" t="inlineStr">
         <is>
-          <t>Industrial data collection and corridor visibility analytics</t>
+          <t>Power distribution utility network visualization and asset tagging</t>
         </is>
       </c>
       <c r="L197" s="18" t="inlineStr">
         <is>
-          <t>High-resolution digital mapping, AI-driven data processing, multi-rotor inspection setups</t>
+          <t>Drone topographic terrain modeling and connected network mapping</t>
         </is>
       </c>
       <c r="M197" s="15" t="inlineStr">
@@ -16929,20 +16933,16 @@
       <c r="O197" s="18" t="inlineStr"/>
       <c r="P197" s="18" t="inlineStr"/>
       <c r="Q197" s="18" t="inlineStr"/>
-      <c r="R197" s="18" t="inlineStr">
-        <is>
-          <t>+91 89026 72625</t>
-        </is>
-      </c>
+      <c r="R197" s="18" t="inlineStr"/>
       <c r="S197" s="17" t="inlineStr">
         <is>
-          <t>falconrise.in</t>
+          <t>cyberswift.com</t>
         </is>
       </c>
       <c r="T197" s="18" t="inlineStr"/>
       <c r="U197" s="15" t="inlineStr">
         <is>
-          <t>+91 / IN</t>
+          <t>+91 / IN; +1 / US</t>
         </is>
       </c>
     </row>
@@ -16952,30 +16952,30 @@
       </c>
       <c r="B198" s="12" t="inlineStr">
         <is>
-          <t>CyberSWIFT Infotech Private Limited</t>
+          <t>BridgeGate Solutions Private Limited</t>
         </is>
       </c>
       <c r="C198" s="13" t="inlineStr">
         <is>
-          <t>cyberswift.com</t>
+          <t>bridgegatesolutions.in</t>
         </is>
       </c>
       <c r="D198" s="11" t="n">
-        <v>2008</v>
+        <v>2025</v>
       </c>
       <c r="E198" s="14" t="inlineStr">
         <is>
-          <t>Kolkata, India</t>
+          <t>Howrah, India</t>
         </is>
       </c>
       <c r="F198" s="14" t="inlineStr">
         <is>
-          <t>NA(United States); APAC(India)</t>
+          <t>APAC(India)</t>
         </is>
       </c>
       <c r="G198" s="14" t="inlineStr">
         <is>
-          <t>India; United States</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H198" s="14" t="inlineStr">
@@ -16985,22 +16985,22 @@
       </c>
       <c r="I198" s="11" t="inlineStr">
         <is>
-          <t>100-500</t>
+          <t>10-50</t>
         </is>
       </c>
       <c r="J198" s="14" t="inlineStr">
         <is>
-          <t>GIS spatial analytics; utility network data mapping</t>
+          <t>Drone utility inspection; geospatial mapping and spatial analytics</t>
         </is>
       </c>
       <c r="K198" s="14" t="inlineStr">
         <is>
-          <t>Power distribution utility network visualization and asset tagging</t>
+          <t>Predictive asset maintenance and corridor risk mitigation for the energy sector</t>
         </is>
       </c>
       <c r="L198" s="14" t="inlineStr">
         <is>
-          <t>Drone topographic terrain modeling and connected network mapping</t>
+          <t>Radiometric thermal drone imaging and automated feature extraction from point clouds</t>
         </is>
       </c>
       <c r="M198" s="11" t="inlineStr">
@@ -17015,13 +17015,13 @@
       <c r="R198" s="14" t="inlineStr"/>
       <c r="S198" s="13" t="inlineStr">
         <is>
-          <t>cyberswift.com</t>
+          <t>bridgegatesolutions.in</t>
         </is>
       </c>
       <c r="T198" s="14" t="inlineStr"/>
       <c r="U198" s="11" t="inlineStr">
         <is>
-          <t>+91 / IN; +1 / US</t>
+          <t>+91 / IN</t>
         </is>
       </c>
     </row>
@@ -17031,20 +17031,20 @@
       </c>
       <c r="B199" s="16" t="inlineStr">
         <is>
-          <t>BridgeGate Solutions Private Limited</t>
+          <t>Sunsky Drone</t>
         </is>
       </c>
       <c r="C199" s="17" t="inlineStr">
         <is>
-          <t>bridgegatesolutions.in</t>
+          <t>sunskydrones.com</t>
         </is>
       </c>
       <c r="D199" s="15" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="E199" s="18" t="inlineStr">
         <is>
-          <t>Howrah, India</t>
+          <t>Kolkata, India</t>
         </is>
       </c>
       <c r="F199" s="18" t="inlineStr">
@@ -17064,22 +17064,22 @@
       </c>
       <c r="I199" s="15" t="inlineStr">
         <is>
-          <t>10-50</t>
+          <t>1-10</t>
         </is>
       </c>
       <c r="J199" s="18" t="inlineStr">
         <is>
-          <t>Drone utility inspection; geospatial mapping and spatial analytics</t>
+          <t>Aerial thermography scans; high-precision LiDAR mapping</t>
         </is>
       </c>
       <c r="K199" s="18" t="inlineStr">
         <is>
-          <t>Predictive asset maintenance and corridor risk mitigation for the energy sector</t>
+          <t>Transmission corridor asset fault identification and structural threat mapping</t>
         </is>
       </c>
       <c r="L199" s="18" t="inlineStr">
         <is>
-          <t>Radiometric thermal drone imaging and automated feature extraction from point clouds</t>
+          <t>LiDAR 3D point cloud reconstructions and drone aerial documentation sensors</t>
         </is>
       </c>
       <c r="M199" s="15" t="inlineStr">
@@ -17094,7 +17094,7 @@
       <c r="R199" s="18" t="inlineStr"/>
       <c r="S199" s="17" t="inlineStr">
         <is>
-          <t>bridgegatesolutions.in</t>
+          <t>sunskydrones.com</t>
         </is>
       </c>
       <c r="T199" s="18" t="inlineStr"/>
@@ -17110,16 +17110,16 @@
       </c>
       <c r="B200" s="12" t="inlineStr">
         <is>
-          <t>Sunsky Drone</t>
+          <t>Stesalit Systems Ltd.</t>
         </is>
       </c>
       <c r="C200" s="13" t="inlineStr">
         <is>
-          <t>sunskydrones.com</t>
+          <t>stesalit-inc.com</t>
         </is>
       </c>
       <c r="D200" s="11" t="n">
-        <v>2023</v>
+        <v>1981</v>
       </c>
       <c r="E200" s="14" t="inlineStr">
         <is>
@@ -17128,12 +17128,12 @@
       </c>
       <c r="F200" s="14" t="inlineStr">
         <is>
-          <t>APAC(India)</t>
+          <t>NA(United States); APAC(India)</t>
         </is>
       </c>
       <c r="G200" s="14" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>India; United States</t>
         </is>
       </c>
       <c r="H200" s="14" t="inlineStr">
@@ -17143,22 +17143,22 @@
       </c>
       <c r="I200" s="11" t="inlineStr">
         <is>
-          <t>1-10</t>
+          <t>50-200</t>
         </is>
       </c>
       <c r="J200" s="14" t="inlineStr">
         <is>
-          <t>Aerial thermography scans; high-precision LiDAR mapping</t>
+          <t>Spatial drone inspections; utility asset integrity management solutions</t>
         </is>
       </c>
       <c r="K200" s="14" t="inlineStr">
         <is>
-          <t>Transmission corridor asset fault identification and structural threat mapping</t>
+          <t>Thermal anomaly mapping and line sag analysis for electric grids</t>
         </is>
       </c>
       <c r="L200" s="14" t="inlineStr">
         <is>
-          <t>LiDAR 3D point cloud reconstructions and drone aerial documentation sensors</t>
+          <t>UAV ultrasonic grid scanners and radiometric thermal payloads</t>
         </is>
       </c>
       <c r="M200" s="11" t="inlineStr">
@@ -17173,32 +17173,32 @@
       <c r="R200" s="14" t="inlineStr"/>
       <c r="S200" s="13" t="inlineStr">
         <is>
-          <t>sunskydrones.com</t>
+          <t>stesalit-inc.com</t>
         </is>
       </c>
       <c r="T200" s="14" t="inlineStr"/>
       <c r="U200" s="11" t="inlineStr">
         <is>
-          <t>+91 / IN</t>
-        </is>
-      </c>
-    </row>
-    <row r="201" ht="33" customHeight="1">
+          <t>+91 / IN; +1 / US</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="46.5" customHeight="1">
       <c r="A201" s="15" t="n">
         <v>196</v>
       </c>
       <c r="B201" s="16" t="inlineStr">
         <is>
-          <t>Stesalit Systems Ltd.</t>
+          <t>Calcutta Drone Academy</t>
         </is>
       </c>
       <c r="C201" s="17" t="inlineStr">
         <is>
-          <t>stesalit-inc.com</t>
+          <t>calcuttadroneacademy.com</t>
         </is>
       </c>
       <c r="D201" s="15" t="n">
-        <v>1981</v>
+        <v>2022</v>
       </c>
       <c r="E201" s="18" t="inlineStr">
         <is>
@@ -17207,12 +17207,12 @@
       </c>
       <c r="F201" s="18" t="inlineStr">
         <is>
-          <t>NA(United States); APAC(India)</t>
+          <t>APAC(India)</t>
         </is>
       </c>
       <c r="G201" s="18" t="inlineStr">
         <is>
-          <t>India; United States</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H201" s="18" t="inlineStr">
@@ -17222,22 +17222,22 @@
       </c>
       <c r="I201" s="15" t="inlineStr">
         <is>
-          <t>50-200</t>
+          <t>5-25</t>
         </is>
       </c>
       <c r="J201" s="18" t="inlineStr">
         <is>
-          <t>Spatial drone inspections; utility asset integrity management solutions</t>
+          <t>Drone operations deployment; industrial inspection services; aerial asset mapping</t>
         </is>
       </c>
       <c r="K201" s="18" t="inlineStr">
         <is>
-          <t>Thermal anomaly mapping and line sag analysis for electric grids</t>
+          <t>Utility structure evaluation flights, roadway inspection data logging, and corridor survey setups.</t>
         </is>
       </c>
       <c r="L201" s="18" t="inlineStr">
         <is>
-          <t>UAV ultrasonic grid scanners and radiometric thermal payloads</t>
+          <t>DGCA-compliant mapping multirotors, photogrammetry tracking suites, and sensor data processing software.</t>
         </is>
       </c>
       <c r="M201" s="15" t="inlineStr">
@@ -17252,32 +17252,32 @@
       <c r="R201" s="18" t="inlineStr"/>
       <c r="S201" s="17" t="inlineStr">
         <is>
-          <t>stesalit-inc.com</t>
+          <t>calcuttadroneacademy.com</t>
         </is>
       </c>
       <c r="T201" s="18" t="inlineStr"/>
       <c r="U201" s="15" t="inlineStr">
         <is>
-          <t>+91 / IN; +1 / US</t>
-        </is>
-      </c>
-    </row>
-    <row r="202" ht="46.5" customHeight="1">
+          <t>+91 / IN</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="33" customHeight="1">
       <c r="A202" s="11" t="n">
         <v>197</v>
       </c>
       <c r="B202" s="12" t="inlineStr">
         <is>
-          <t>Calcutta Drone Academy</t>
+          <t>Drones Tech Lab</t>
         </is>
       </c>
       <c r="C202" s="13" t="inlineStr">
         <is>
-          <t>calcuttadroneacademy.com</t>
+          <t>dronestechlab.com</t>
         </is>
       </c>
       <c r="D202" s="11" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="E202" s="14" t="inlineStr">
         <is>
@@ -17301,22 +17301,22 @@
       </c>
       <c r="I202" s="11" t="inlineStr">
         <is>
-          <t>5-25</t>
+          <t>50-200</t>
         </is>
       </c>
       <c r="J202" s="14" t="inlineStr">
         <is>
-          <t>Drone operations deployment; industrial inspection services; aerial asset mapping</t>
+          <t>Unmanned aerial vehicles; drone inspection software</t>
         </is>
       </c>
       <c r="K202" s="14" t="inlineStr">
         <is>
-          <t>Utility structure evaluation flights, roadway inspection data logging, and corridor survey setups.</t>
+          <t>Power line inspection with thermal sensors and high-resolution corridor mapping</t>
         </is>
       </c>
       <c r="L202" s="14" t="inlineStr">
         <is>
-          <t>DGCA-compliant mapping multirotors, photogrammetry tracking suites, and sensor data processing software.</t>
+          <t>Thermal sensor drone fault detection; LiDAR asset mapping</t>
         </is>
       </c>
       <c r="M202" s="11" t="inlineStr">
@@ -17328,10 +17328,14 @@
       <c r="O202" s="14" t="inlineStr"/>
       <c r="P202" s="14" t="inlineStr"/>
       <c r="Q202" s="14" t="inlineStr"/>
-      <c r="R202" s="14" t="inlineStr"/>
+      <c r="R202" s="14" t="inlineStr">
+        <is>
+          <t>+91 99037 44335</t>
+        </is>
+      </c>
       <c r="S202" s="13" t="inlineStr">
         <is>
-          <t>calcuttadroneacademy.com</t>
+          <t>dronestechlab.com</t>
         </is>
       </c>
       <c r="T202" s="14" t="inlineStr"/>
@@ -17341,22 +17345,22 @@
         </is>
       </c>
     </row>
-    <row r="203" ht="33" customHeight="1">
+    <row r="203" ht="46.5" customHeight="1">
       <c r="A203" s="15" t="n">
         <v>198</v>
       </c>
       <c r="B203" s="16" t="inlineStr">
         <is>
-          <t>Drones Tech Lab</t>
+          <t>Maverick Drones and Technologies Private Limited</t>
         </is>
       </c>
       <c r="C203" s="17" t="inlineStr">
         <is>
-          <t>dronestechlab.com</t>
+          <t>mavdrones.com</t>
         </is>
       </c>
       <c r="D203" s="15" t="n">
-        <v>2016</v>
+        <v>2020</v>
       </c>
       <c r="E203" s="18" t="inlineStr">
         <is>
@@ -17380,22 +17384,22 @@
       </c>
       <c r="I203" s="15" t="inlineStr">
         <is>
-          <t>50-200</t>
+          <t>11-25</t>
         </is>
       </c>
       <c r="J203" s="18" t="inlineStr">
         <is>
-          <t>Unmanned aerial vehicles; drone inspection software</t>
+          <t>Commercial drone operations; aerial inspection data acquisition; corridor scanning</t>
         </is>
       </c>
       <c r="K203" s="18" t="inlineStr">
         <is>
-          <t>Power line inspection with thermal sensors and high-resolution corridor mapping</t>
+          <t>Customized UAV data collection across complex grid infrastructure and high-voltage transmission rights-of-way</t>
         </is>
       </c>
       <c r="L203" s="18" t="inlineStr">
         <is>
-          <t>Thermal sensor drone fault detection; LiDAR asset mapping</t>
+          <t>DJI Matrice platforms, thermal sensor integrations, and high-definition visual payloads</t>
         </is>
       </c>
       <c r="M203" s="15" t="inlineStr">
@@ -17403,18 +17407,22 @@
           <t>Both</t>
         </is>
       </c>
-      <c r="N203" s="18" t="inlineStr"/>
-      <c r="O203" s="18" t="inlineStr"/>
+      <c r="N203" s="18" t="inlineStr">
+        <is>
+          <t>Pradipta Vaskar Mukherjee</t>
+        </is>
+      </c>
+      <c r="O203" s="18" t="inlineStr">
+        <is>
+          <t>Founder &amp; Chief Executive Officer</t>
+        </is>
+      </c>
       <c r="P203" s="18" t="inlineStr"/>
       <c r="Q203" s="18" t="inlineStr"/>
-      <c r="R203" s="18" t="inlineStr">
-        <is>
-          <t>+91 99037 44335</t>
-        </is>
-      </c>
+      <c r="R203" s="18" t="inlineStr"/>
       <c r="S203" s="17" t="inlineStr">
         <is>
-          <t>dronestechlab.com</t>
+          <t>mavdrones.com</t>
         </is>
       </c>
       <c r="T203" s="18" t="inlineStr"/>
@@ -17430,16 +17438,16 @@
       </c>
       <c r="B204" s="12" t="inlineStr">
         <is>
-          <t>Maverick Drones and Technologies Private Limited</t>
+          <t>QuillAir Pvt. Ltd.</t>
         </is>
       </c>
       <c r="C204" s="13" t="inlineStr">
         <is>
-          <t>mavdrones.com</t>
+          <t>quillair.in</t>
         </is>
       </c>
       <c r="D204" s="11" t="n">
-        <v>2020</v>
+        <v>2025</v>
       </c>
       <c r="E204" s="14" t="inlineStr">
         <is>
@@ -17463,48 +17471,56 @@
       </c>
       <c r="I204" s="11" t="inlineStr">
         <is>
-          <t>11-25</t>
+          <t>11-50</t>
         </is>
       </c>
       <c r="J204" s="14" t="inlineStr">
         <is>
-          <t>Commercial drone operations; aerial inspection data acquisition; corridor scanning</t>
+          <t>Drone-as-a-Service (DaaS); aerial infrastructure audits; environmental canopy tracking</t>
         </is>
       </c>
       <c r="K204" s="14" t="inlineStr">
         <is>
-          <t>Customized UAV data collection across complex grid infrastructure and high-voltage transmission rights-of-way</t>
+          <t>AI-powered custom unmanned flight operations and localized survey-grade telemetry analytics for commercial utilities</t>
         </is>
       </c>
       <c r="L204" s="14" t="inlineStr">
         <is>
-          <t>DJI Matrice platforms, thermal sensor integrations, and high-definition visual payloads</t>
+          <t>Long-range fixed-wing VTOL aircraft, bespoke payload data interfaces, and embedded web dashboards</t>
         </is>
       </c>
       <c r="M204" s="11" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Offline</t>
         </is>
       </c>
       <c r="N204" s="14" t="inlineStr">
         <is>
-          <t>Pradipta Vaskar Mukherjee</t>
+          <t>Aryaman Agarwal</t>
         </is>
       </c>
       <c r="O204" s="14" t="inlineStr">
         <is>
-          <t>Founder &amp; Chief Executive Officer</t>
-        </is>
-      </c>
-      <c r="P204" s="14" t="inlineStr"/>
+          <t>Director &amp; Co-Founder</t>
+        </is>
+      </c>
+      <c r="P204" s="13" t="inlineStr">
+        <is>
+          <t>info@quillair.in</t>
+        </is>
+      </c>
       <c r="Q204" s="14" t="inlineStr"/>
       <c r="R204" s="14" t="inlineStr"/>
       <c r="S204" s="13" t="inlineStr">
         <is>
-          <t>mavdrones.com</t>
-        </is>
-      </c>
-      <c r="T204" s="14" t="inlineStr"/>
+          <t>quillair.in</t>
+        </is>
+      </c>
+      <c r="T204" s="13" t="inlineStr">
+        <is>
+          <t>info@quillair.in</t>
+        </is>
+      </c>
       <c r="U204" s="11" t="inlineStr">
         <is>
           <t>+91 / IN</t>
@@ -17517,16 +17533,16 @@
       </c>
       <c r="B205" s="16" t="inlineStr">
         <is>
-          <t>QuillAir Pvt. Ltd.</t>
+          <t>Federal Synergies (India) Private Limited</t>
         </is>
       </c>
       <c r="C205" s="17" t="inlineStr">
         <is>
-          <t>quillair.in</t>
+          <t>federalsynergies.com</t>
         </is>
       </c>
       <c r="D205" s="15" t="n">
-        <v>2025</v>
+        <v>2008</v>
       </c>
       <c r="E205" s="18" t="inlineStr">
         <is>
@@ -17555,17 +17571,17 @@
       </c>
       <c r="J205" s="18" t="inlineStr">
         <is>
-          <t>Drone-as-a-Service (DaaS); aerial infrastructure audits; environmental canopy tracking</t>
+          <t>Power utility field engineering; GIS network solutions; smart system integrations</t>
         </is>
       </c>
       <c r="K205" s="18" t="inlineStr">
         <is>
-          <t>AI-powered custom unmanned flight operations and localized survey-grade telemetry analytics for commercial utilities</t>
+          <t>End-to-end grid asset indexing, digital field survey management, and power distribution optimizations</t>
         </is>
       </c>
       <c r="L205" s="18" t="inlineStr">
         <is>
-          <t>Long-range fixed-wing VTOL aircraft, bespoke payload data interfaces, and embedded web dashboards</t>
+          <t>METX tracking systems, smart utility analytics, and georeferenced survey mapping datasets</t>
         </is>
       </c>
       <c r="M205" s="15" t="inlineStr">
@@ -17575,29 +17591,29 @@
       </c>
       <c r="N205" s="18" t="inlineStr">
         <is>
-          <t>Aryaman Agarwal</t>
+          <t>Prayush Poddar</t>
         </is>
       </c>
       <c r="O205" s="18" t="inlineStr">
         <is>
-          <t>Director &amp; Co-Founder</t>
+          <t>Managing Director / Owner</t>
         </is>
       </c>
       <c r="P205" s="17" t="inlineStr">
         <is>
-          <t>info@quillair.in</t>
+          <t>info@federalsynergies.com</t>
         </is>
       </c>
       <c r="Q205" s="18" t="inlineStr"/>
       <c r="R205" s="18" t="inlineStr"/>
       <c r="S205" s="17" t="inlineStr">
         <is>
-          <t>quillair.in</t>
+          <t>federalsynergies.com</t>
         </is>
       </c>
       <c r="T205" s="17" t="inlineStr">
         <is>
-          <t>info@quillair.in</t>
+          <t>info@federalsynergies.com</t>
         </is>
       </c>
       <c r="U205" s="15" t="inlineStr">
@@ -17606,103 +17622,9 @@
         </is>
       </c>
     </row>
-    <row r="206" ht="46.5" customHeight="1">
-      <c r="A206" s="11" t="n">
-        <v>201</v>
-      </c>
-      <c r="B206" s="12" t="inlineStr">
-        <is>
-          <t>Federal Synergies (India) Private Limited</t>
-        </is>
-      </c>
-      <c r="C206" s="13" t="inlineStr">
-        <is>
-          <t>federalsynergies.com</t>
-        </is>
-      </c>
-      <c r="D206" s="11" t="n">
-        <v>2008</v>
-      </c>
-      <c r="E206" s="14" t="inlineStr">
-        <is>
-          <t>Kolkata, India</t>
-        </is>
-      </c>
-      <c r="F206" s="14" t="inlineStr">
-        <is>
-          <t>APAC(India)</t>
-        </is>
-      </c>
-      <c r="G206" s="14" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="H206" s="14" t="inlineStr">
-        <is>
-          <t>Private Company</t>
-        </is>
-      </c>
-      <c r="I206" s="11" t="inlineStr">
-        <is>
-          <t>11-50</t>
-        </is>
-      </c>
-      <c r="J206" s="14" t="inlineStr">
-        <is>
-          <t>Power utility field engineering; GIS network solutions; smart system integrations</t>
-        </is>
-      </c>
-      <c r="K206" s="14" t="inlineStr">
-        <is>
-          <t>End-to-end grid asset indexing, digital field survey management, and power distribution optimizations</t>
-        </is>
-      </c>
-      <c r="L206" s="14" t="inlineStr">
-        <is>
-          <t>METX tracking systems, smart utility analytics, and georeferenced survey mapping datasets</t>
-        </is>
-      </c>
-      <c r="M206" s="11" t="inlineStr">
-        <is>
-          <t>Offline</t>
-        </is>
-      </c>
-      <c r="N206" s="14" t="inlineStr">
-        <is>
-          <t>Prayush Poddar</t>
-        </is>
-      </c>
-      <c r="O206" s="14" t="inlineStr">
-        <is>
-          <t>Managing Director / Owner</t>
-        </is>
-      </c>
-      <c r="P206" s="13" t="inlineStr">
-        <is>
-          <t>info@federalsynergies.com</t>
-        </is>
-      </c>
-      <c r="Q206" s="14" t="inlineStr"/>
-      <c r="R206" s="14" t="inlineStr"/>
-      <c r="S206" s="13" t="inlineStr">
-        <is>
-          <t>federalsynergies.com</t>
-        </is>
-      </c>
-      <c r="T206" s="13" t="inlineStr">
-        <is>
-          <t>info@federalsynergies.com</t>
-        </is>
-      </c>
-      <c r="U206" s="11" t="inlineStr">
-        <is>
-          <t>+91 / IN</t>
-        </is>
-      </c>
-    </row>
+    <row r="206" ht="42" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="A5:U206"/>
+  <autoFilter ref="A5:U205"/>
   <mergeCells count="4">
     <mergeCell ref="A1:U1"/>
     <mergeCell ref="A4:U4"/>
@@ -18038,11 +17960,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C141" r:id="rId326"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S141" r:id="rId327"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C142" r:id="rId328"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S142" r:id="rId329"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C143" r:id="rId330"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P143" r:id="rId331"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S143" r:id="rId332"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T143" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P142" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S142" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T142" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C143" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S143" r:id="rId333"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C144" r:id="rId334"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S144" r:id="rId335"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C145" r:id="rId336"/>
@@ -18052,77 +17974,77 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C147" r:id="rId340"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S147" r:id="rId341"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C148" r:id="rId342"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S148" r:id="rId343"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C149" r:id="rId344"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P149" r:id="rId345"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S149" r:id="rId346"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T149" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P148" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S148" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T148" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C149" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S149" r:id="rId347"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C150" r:id="rId348"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S150" r:id="rId349"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C151" r:id="rId350"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S151" r:id="rId351"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T151" r:id="rId352"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C152" r:id="rId353"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S152" r:id="rId354"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T152" r:id="rId355"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C153" r:id="rId356"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S153" r:id="rId357"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T153" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T150" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C151" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S151" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T151" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C152" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S152" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T152" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C153" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S153" r:id="rId358"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C154" r:id="rId359"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S154" r:id="rId360"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C155" r:id="rId361"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S155" r:id="rId362"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C156" r:id="rId363"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P156" r:id="rId364"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S156" r:id="rId365"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T156" r:id="rId366"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C157" r:id="rId367"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P157" r:id="rId368"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S157" r:id="rId369"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T157" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P155" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S155" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T155" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C156" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P156" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S156" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T156" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C157" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S157" r:id="rId370"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C158" r:id="rId371"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S158" r:id="rId372"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C159" r:id="rId373"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S159" r:id="rId374"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C160" r:id="rId375"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P160" r:id="rId376"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S160" r:id="rId377"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T160" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P159" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S159" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T159" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C160" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S160" r:id="rId378"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C161" r:id="rId379"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S161" r:id="rId380"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C162" r:id="rId381"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S162" r:id="rId382"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T162" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T161" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C162" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S162" r:id="rId383"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C163" r:id="rId384"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S163" r:id="rId385"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C164" r:id="rId386"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S164" r:id="rId387"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T164" r:id="rId388"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C165" r:id="rId389"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P165" r:id="rId390"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S165" r:id="rId391"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T165" r:id="rId392"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C166" r:id="rId393"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P166" r:id="rId394"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S166" r:id="rId395"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T166" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T163" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C164" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P164" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S164" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T164" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C165" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P165" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S165" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T165" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C166" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S166" r:id="rId396"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C167" r:id="rId397"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S167" r:id="rId398"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C168" r:id="rId399"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S168" r:id="rId400"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C169" r:id="rId401"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S169" r:id="rId402"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T169" r:id="rId403"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C170" r:id="rId404"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S170" r:id="rId405"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T170" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T168" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C169" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S169" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T169" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C170" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S170" r:id="rId406"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C171" r:id="rId407"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S171" r:id="rId408"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C172" r:id="rId409"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S172" r:id="rId410"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C173" r:id="rId411"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S173" r:id="rId412"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T173" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T172" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C173" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S173" r:id="rId413"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C174" r:id="rId414"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S174" r:id="rId415"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C175" r:id="rId416"/>
@@ -18139,15 +18061,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S180" r:id="rId427"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C181" r:id="rId428"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S181" r:id="rId429"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C182" r:id="rId430"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S182" r:id="rId431"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T182" r:id="rId432"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C183" r:id="rId433"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S183" r:id="rId434"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T183" r:id="rId435"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C184" r:id="rId436"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S184" r:id="rId437"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T184" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T181" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C182" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S182" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T182" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C183" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S183" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T183" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C184" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S184" r:id="rId438"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C185" r:id="rId439"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S185" r:id="rId440"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C186" r:id="rId441"/>
@@ -18166,14 +18088,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S192" r:id="rId454"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C193" r:id="rId455"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S193" r:id="rId456"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C194" r:id="rId457"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S194" r:id="rId458"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T194" r:id="rId459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T193" r:id="rId457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C194" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S194" r:id="rId459"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C195" r:id="rId460"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S195" r:id="rId461"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C196" r:id="rId462"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S196" r:id="rId463"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T196" r:id="rId464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T195" r:id="rId462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C196" r:id="rId463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S196" r:id="rId464"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C197" r:id="rId465"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S197" r:id="rId466"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C198" r:id="rId467"/>
@@ -18189,15 +18111,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C203" r:id="rId477"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S203" r:id="rId478"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C204" r:id="rId479"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S204" r:id="rId480"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C205" r:id="rId481"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P205" r:id="rId482"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S205" r:id="rId483"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T205" r:id="rId484"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C206" r:id="rId485"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P206" r:id="rId486"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S206" r:id="rId487"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T206" r:id="rId488"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P204" r:id="rId480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S204" r:id="rId481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T204" r:id="rId482"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C205" r:id="rId483"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P205" r:id="rId484"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S205" r:id="rId485"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T205" r:id="rId486"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
